--- a/proposal/collaboration/collaboration_vinuesa.xlsx
+++ b/proposal/collaboration/collaboration_vinuesa.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kth-my.sharepoint.com/personal/rvinuesa_ug_kth_se/Documents/Skrivbordet/FUNDING OPPORTUNITIES/DoE Genesis/Argonne/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/misunmin/proj/genesis21b/proposal/collaboration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="11_756FD2B3F0365D6AE8EC972EAD278D7FE844A4BE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71C28A3A-ECA7-4363-81AE-6E2FB1BAFED2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA0AD59-726D-0C42-9FBC-EE932D6398F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4320" yWindow="660" windowWidth="22780" windowHeight="14540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="3" r:id="rId1"/>
@@ -350,9 +350,6 @@
     <t>Barcelona Supercomputing Center</t>
   </si>
   <si>
-    <t>Applicant Organization:</t>
-  </si>
-  <si>
     <t>Vinuesa, Ricardo</t>
   </si>
   <si>
@@ -1517,9 +1514,6 @@
     <t>Bernat</t>
   </si>
   <si>
-    <t xml:space="preserve">University of Michigan </t>
-  </si>
-  <si>
     <t>Cattafesta</t>
   </si>
   <si>
@@ -1548,6 +1542,12 @@
   </si>
   <si>
     <t>Los Alamons National Lab</t>
+  </si>
+  <si>
+    <t>Argonne National Laboratory</t>
+  </si>
+  <si>
+    <t>Min, Misun</t>
   </si>
 </sst>
 </file>
@@ -2079,13 +2079,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2099,12 +2105,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2423,18 +2423,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="128.6328125" customWidth="1"/>
+    <col min="1" max="1" width="128.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="391.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="395" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="17"/>
     </row>
   </sheetData>
@@ -2446,63 +2446,63 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="22.6328125" customWidth="1"/>
+    <col min="1" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="3" width="24" style="2" customWidth="1"/>
-    <col min="4" max="4" width="45.6328125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="45.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="39" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="39"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="37" t="s">
+      <c r="D1" s="40"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="39" t="s">
+      <c r="B2" s="39"/>
+      <c r="C2" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="39"/>
-    </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="37" t="s">
+      <c r="D2" s="40"/>
+    </row>
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="39" t="s">
+      <c r="B3" s="39"/>
+      <c r="C3" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="39"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="37" t="s">
+      <c r="D3" s="40"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="39" t="s">
+      <c r="B4" s="39"/>
+      <c r="C4" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="39"/>
-    </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="44" t="s">
+      <c r="D4" s="40"/>
+    </row>
+    <row r="5" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="45"/>
+      <c r="B6" s="38"/>
       <c r="C6" s="30"/>
       <c r="D6" s="31"/>
     </row>
-    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
         <v>9</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="21" t="s">
         <v>67</v>
       </c>
@@ -2528,115 +2528,115 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="25"/>
       <c r="B9" s="18"/>
       <c r="C9" s="19"/>
       <c r="D9" s="26"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="25"/>
       <c r="B10" s="18"/>
       <c r="C10" s="19"/>
       <c r="D10" s="26"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="25"/>
       <c r="B11" s="18"/>
       <c r="C11" s="19"/>
       <c r="D11" s="26"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="25"/>
       <c r="B12" s="18"/>
       <c r="C12" s="19"/>
       <c r="D12" s="26"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="25"/>
       <c r="B13" s="18"/>
       <c r="C13" s="19"/>
       <c r="D13" s="26"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="25"/>
       <c r="B14" s="18"/>
       <c r="C14" s="19"/>
       <c r="D14" s="26"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="25"/>
       <c r="B15" s="18"/>
       <c r="C15" s="19"/>
       <c r="D15" s="26"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="25"/>
       <c r="B16" s="18"/>
       <c r="C16" s="19"/>
       <c r="D16" s="26"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="25"/>
       <c r="B17" s="18"/>
       <c r="C17" s="19"/>
       <c r="D17" s="26"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="25"/>
       <c r="B18" s="18"/>
       <c r="C18" s="19"/>
       <c r="D18" s="26"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="25"/>
       <c r="B19" s="18"/>
       <c r="C19" s="19"/>
       <c r="D19" s="26"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="25"/>
       <c r="B20" s="18"/>
       <c r="C20" s="19"/>
       <c r="D20" s="26"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="25"/>
       <c r="B21" s="18"/>
       <c r="C21" s="19"/>
       <c r="D21" s="26"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="25"/>
       <c r="B22" s="18"/>
       <c r="C22" s="19"/>
       <c r="D22" s="26"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="25"/>
       <c r="B23" s="18"/>
       <c r="C23" s="19"/>
       <c r="D23" s="26"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="25"/>
       <c r="B24" s="18"/>
       <c r="C24" s="19"/>
       <c r="D24" s="26"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="25"/>
       <c r="B25" s="18"/>
       <c r="C25" s="19"/>
       <c r="D25" s="26"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="25"/>
       <c r="B26" s="18"/>
       <c r="C26" s="19"/>
       <c r="D26" s="26"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="25"/>
       <c r="B27" s="18"/>
       <c r="C27" s="19"/>
@@ -2670,77 +2670,77 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H1048576"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="22.6328125" customWidth="1"/>
-    <col min="3" max="4" width="22.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1796875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="59.453125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="35.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.453125" customWidth="1"/>
+    <col min="1" max="2" width="22.6640625" customWidth="1"/>
+    <col min="3" max="4" width="22.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="59.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="40" t="s">
+        <v>488</v>
+      </c>
+      <c r="D1" s="40"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="D2" s="40"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="39"/>
+      <c r="C3" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="39" t="s">
-        <v>479</v>
-      </c>
-      <c r="D1" s="39"/>
-      <c r="E1" s="3"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="39" t="s">
+      <c r="D3" s="40"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="39"/>
+      <c r="C4" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="39"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="39" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" s="39"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" s="39"/>
+      <c r="D4" s="40"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="40" t="s">
+    <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="42" t="str">
+      <c r="B6" s="43"/>
+      <c r="C6" s="44" t="str">
         <f>"Collaborator Table - "&amp;C1&amp;" ("&amp;C2&amp;")"</f>
-        <v>Collaborator Table - University of Michigan  (Vinuesa, Ricardo)</v>
-      </c>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="43"/>
-    </row>
-    <row r="7" spans="1:8" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>Collaborator Table - Argonne National Laboratory (Min, Misun)</v>
+      </c>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="45"/>
+    </row>
+    <row r="7" spans="1:8" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>9</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
         <v>67</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="B9" s="5"/>
       <c r="C9" s="35" t="s">
@@ -2801,36 +2801,36 @@
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H9" s="7">
         <v>2024</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
       <c r="C10" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" s="32" t="s">
         <v>94</v>
-      </c>
-      <c r="D10" s="32" t="s">
-        <v>95</v>
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="35" t="s">
         <v>82</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H10" s="7">
         <v>2024</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="36" t="s">
@@ -2850,7 +2850,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="35" t="s">
@@ -2870,7 +2870,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
       <c r="B13" s="5"/>
       <c r="C13" s="36" t="s">
@@ -2884,304 +2884,304 @@
         <v>69</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H13" s="7">
         <v>2024</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
       <c r="B14" s="5"/>
       <c r="C14" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="32" t="s">
         <v>98</v>
-      </c>
-      <c r="D14" s="32" t="s">
-        <v>99</v>
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="36" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H14" s="7">
         <v>2023</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
       <c r="B15" s="5"/>
       <c r="C15" s="36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H15" s="7">
         <v>2021</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
       <c r="B16" s="5"/>
       <c r="C16" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" s="32" t="s">
         <v>102</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>103</v>
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H16" s="7">
         <v>2024</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
       <c r="B17" s="5"/>
       <c r="C17" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="32" t="s">
         <v>104</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>105</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="36" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H17" s="7">
         <v>2024</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="4"/>
       <c r="B18" s="5"/>
       <c r="C18" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" s="32" t="s">
         <v>107</v>
-      </c>
-      <c r="D18" s="32" t="s">
-        <v>108</v>
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H18" s="7">
         <v>2025</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
       <c r="B19" s="5"/>
       <c r="C19" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="32" t="s">
         <v>110</v>
-      </c>
-      <c r="D19" s="32" t="s">
-        <v>111</v>
       </c>
       <c r="E19" s="32"/>
       <c r="F19" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H19" s="7">
         <v>2021</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
       <c r="B20" s="5"/>
       <c r="C20" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" s="32" t="s">
         <v>112</v>
-      </c>
-      <c r="D20" s="32" t="s">
-        <v>113</v>
       </c>
       <c r="E20" s="32"/>
       <c r="F20" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H20" s="7">
         <v>2025</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
       <c r="B21" s="5"/>
       <c r="C21" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="D21" s="32" t="s">
         <v>114</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>115</v>
       </c>
       <c r="E21" s="32"/>
       <c r="F21" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H21" s="7">
         <v>2025</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="B22" s="5"/>
       <c r="C22" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="D22" s="32" t="s">
         <v>116</v>
-      </c>
-      <c r="D22" s="32" t="s">
-        <v>117</v>
       </c>
       <c r="E22" s="32"/>
       <c r="F22" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H22" s="7">
         <v>2025</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
       <c r="B23" s="5"/>
       <c r="C23" s="35" t="s">
         <v>39</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H23" s="7">
         <v>2025</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="4"/>
       <c r="B24" s="5"/>
       <c r="C24" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>119</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>120</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="36" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H24" s="7">
         <v>2025</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
       <c r="B25" s="5"/>
       <c r="C25" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25" s="32" t="s">
         <v>122</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>123</v>
       </c>
       <c r="E25" s="32"/>
       <c r="F25" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H25" s="7">
         <v>2025</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="4"/>
       <c r="B26" s="5"/>
       <c r="C26" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="32" t="s">
         <v>124</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>125</v>
       </c>
       <c r="E26" s="32"/>
       <c r="F26" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H26" s="7">
         <v>2025</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
       <c r="B27" s="5"/>
       <c r="C27" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="D27" s="32" t="s">
         <v>126</v>
-      </c>
-      <c r="D27" s="32" t="s">
-        <v>127</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H27" s="7">
         <v>2025</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
       <c r="B28" s="5"/>
       <c r="C28" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28" s="32" t="s">
         <v>128</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>129</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>20</v>
@@ -3190,57 +3190,57 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
       <c r="C29" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E29" s="32"/>
       <c r="F29" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H29" s="7">
         <v>2025</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="4"/>
       <c r="B30" s="5"/>
       <c r="C30" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="D30" s="32" t="s">
         <v>131</v>
-      </c>
-      <c r="D30" s="32" t="s">
-        <v>132</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H30" s="7">
         <v>2025</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="4"/>
       <c r="B31" s="5"/>
       <c r="C31" s="36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D31" s="32" t="s">
         <v>37</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>20</v>
@@ -3249,58 +3249,58 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
       <c r="B32" s="5"/>
       <c r="C32" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="D32" s="32" t="s">
         <v>134</v>
-      </c>
-      <c r="D32" s="32" t="s">
-        <v>135</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H32" s="7">
         <v>2025</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="4"/>
       <c r="B33" s="5"/>
       <c r="C33" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="D33" s="32" t="s">
         <v>136</v>
-      </c>
-      <c r="D33" s="32" t="s">
-        <v>137</v>
       </c>
       <c r="E33" s="32"/>
       <c r="F33" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H33" s="7">
         <v>2025</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
       <c r="B34" s="5"/>
       <c r="C34" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="D34" s="32" t="s">
         <v>138</v>
-      </c>
-      <c r="D34" s="32" t="s">
-        <v>139</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>18</v>
@@ -3309,38 +3309,38 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
       <c r="B35" s="5"/>
       <c r="C35" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="D35" s="32" t="s">
         <v>141</v>
-      </c>
-      <c r="D35" s="32" t="s">
-        <v>142</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H35" s="7">
         <v>2025</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
       <c r="B36" s="5"/>
       <c r="C36" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="D36" s="32" t="s">
         <v>143</v>
-      </c>
-      <c r="D36" s="32" t="s">
-        <v>144</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>20</v>
@@ -3349,18 +3349,18 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
       <c r="B37" s="5"/>
       <c r="C37" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="D37" s="32" t="s">
         <v>146</v>
-      </c>
-      <c r="D37" s="32" t="s">
-        <v>147</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="36" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>20</v>
@@ -3369,18 +3369,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
       <c r="B38" s="5"/>
       <c r="C38" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="D38" s="32" t="s">
         <v>149</v>
-      </c>
-      <c r="D38" s="32" t="s">
-        <v>150</v>
       </c>
       <c r="E38" s="32"/>
       <c r="F38" s="36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>20</v>
@@ -3389,18 +3389,18 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
       <c r="B39" s="5"/>
       <c r="C39" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="D39" s="32" t="s">
         <v>152</v>
-      </c>
-      <c r="D39" s="32" t="s">
-        <v>153</v>
       </c>
       <c r="E39" s="32"/>
       <c r="F39" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>20</v>
@@ -3409,18 +3409,18 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="4"/>
       <c r="B40" s="5"/>
       <c r="C40" s="35" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D40" s="32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E40" s="32"/>
       <c r="F40" s="35" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>20</v>
@@ -3429,18 +3429,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
       <c r="B41" s="5"/>
       <c r="C41" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="D41" s="32" t="s">
         <v>156</v>
-      </c>
-      <c r="D41" s="32" t="s">
-        <v>157</v>
       </c>
       <c r="E41" s="32"/>
       <c r="F41" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>20</v>
@@ -3449,38 +3449,38 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="4"/>
       <c r="B42" s="5"/>
       <c r="C42" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="D42" s="32" t="s">
         <v>158</v>
-      </c>
-      <c r="D42" s="32" t="s">
-        <v>159</v>
       </c>
       <c r="E42" s="32"/>
       <c r="F42" s="35" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H42" s="7">
         <v>2025</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="4"/>
       <c r="B43" s="5"/>
       <c r="C43" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="D43" s="32" t="s">
         <v>161</v>
-      </c>
-      <c r="D43" s="32" t="s">
-        <v>162</v>
       </c>
       <c r="E43" s="32"/>
       <c r="F43" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>20</v>
@@ -3489,58 +3489,58 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="4"/>
       <c r="B44" s="5"/>
       <c r="C44" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="D44" s="32" t="s">
         <v>163</v>
-      </c>
-      <c r="D44" s="32" t="s">
-        <v>164</v>
       </c>
       <c r="E44" s="32"/>
       <c r="F44" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H44" s="7">
         <v>2025</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
       <c r="B45" s="5"/>
       <c r="C45" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="D45" s="32" t="s">
         <v>165</v>
-      </c>
-      <c r="D45" s="32" t="s">
-        <v>166</v>
       </c>
       <c r="E45" s="32"/>
       <c r="F45" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H45" s="7">
         <v>2025</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="4"/>
       <c r="B46" s="5"/>
       <c r="C46" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="D46" s="32" t="s">
         <v>167</v>
-      </c>
-      <c r="D46" s="32" t="s">
-        <v>168</v>
       </c>
       <c r="E46" s="32"/>
       <c r="F46" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>20</v>
@@ -3549,158 +3549,158 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="4"/>
       <c r="B47" s="5"/>
       <c r="C47" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="D47" s="32" t="s">
         <v>169</v>
-      </c>
-      <c r="D47" s="32" t="s">
-        <v>170</v>
       </c>
       <c r="E47" s="32"/>
       <c r="F47" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H47" s="7">
         <v>2022</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
       <c r="B48" s="5"/>
       <c r="C48" s="35" t="s">
+        <v>170</v>
+      </c>
+      <c r="D48" s="32" t="s">
         <v>171</v>
-      </c>
-      <c r="D48" s="32" t="s">
-        <v>172</v>
       </c>
       <c r="E48" s="32"/>
       <c r="F48" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H48" s="7">
         <v>2021</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="4"/>
       <c r="B49" s="5"/>
       <c r="C49" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="D49" s="32" t="s">
         <v>173</v>
-      </c>
-      <c r="D49" s="32" t="s">
-        <v>174</v>
       </c>
       <c r="E49" s="32"/>
       <c r="F49" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H49" s="7">
         <v>2023</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
       <c r="B50" s="5"/>
       <c r="C50" s="33" t="s">
         <v>31</v>
       </c>
       <c r="D50" s="33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E50" s="33"/>
       <c r="F50" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H50" s="7">
         <v>2024</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="4"/>
       <c r="B51" s="5"/>
       <c r="C51" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="D51" s="33" t="s">
         <v>176</v>
-      </c>
-      <c r="D51" s="33" t="s">
-        <v>177</v>
       </c>
       <c r="E51" s="33"/>
       <c r="F51" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H51" s="7">
         <v>2023</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="4"/>
       <c r="B52" s="5"/>
       <c r="C52" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="D52" s="33" t="s">
         <v>178</v>
-      </c>
-      <c r="D52" s="33" t="s">
-        <v>179</v>
       </c>
       <c r="E52" s="33"/>
       <c r="F52" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H52" s="7">
         <v>2024</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
       <c r="B53" s="5"/>
       <c r="C53" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="D53" s="33" t="s">
         <v>180</v>
-      </c>
-      <c r="D53" s="33" t="s">
-        <v>181</v>
       </c>
       <c r="E53" s="33"/>
       <c r="F53" s="33" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H53" s="7">
         <v>2024</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
       <c r="B54" s="5"/>
       <c r="C54" s="33" t="s">
+        <v>182</v>
+      </c>
+      <c r="D54" s="33" t="s">
         <v>183</v>
-      </c>
-      <c r="D54" s="33" t="s">
-        <v>184</v>
       </c>
       <c r="E54" s="33"/>
       <c r="F54" s="33" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G54" s="33" t="s">
         <v>18</v>
@@ -3709,18 +3709,18 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="4"/>
       <c r="B55" s="5"/>
       <c r="C55" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="D55" s="33" t="s">
         <v>186</v>
-      </c>
-      <c r="D55" s="33" t="s">
-        <v>187</v>
       </c>
       <c r="E55" s="33"/>
       <c r="F55" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G55" s="33" t="s">
         <v>18</v>
@@ -3729,18 +3729,18 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="4"/>
       <c r="B56" s="5"/>
       <c r="C56" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="D56" s="33" t="s">
         <v>188</v>
-      </c>
-      <c r="D56" s="33" t="s">
-        <v>189</v>
       </c>
       <c r="E56" s="33"/>
       <c r="F56" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G56" s="33" t="s">
         <v>18</v>
@@ -3749,18 +3749,18 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="4"/>
       <c r="B57" s="5"/>
       <c r="C57" s="33" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D57" s="33" t="s">
         <v>60</v>
       </c>
       <c r="E57" s="33"/>
       <c r="F57" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G57" s="33" t="s">
         <v>18</v>
@@ -3769,18 +3769,18 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="4"/>
       <c r="B58" s="5"/>
       <c r="C58" s="33" t="s">
+        <v>191</v>
+      </c>
+      <c r="D58" s="33" t="s">
         <v>192</v>
-      </c>
-      <c r="D58" s="33" t="s">
-        <v>193</v>
       </c>
       <c r="E58" s="33"/>
       <c r="F58" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G58" s="33" t="s">
         <v>18</v>
@@ -3789,18 +3789,18 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="4"/>
       <c r="B59" s="5"/>
       <c r="C59" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="D59" s="32" t="s">
         <v>194</v>
-      </c>
-      <c r="D59" s="32" t="s">
-        <v>195</v>
       </c>
       <c r="E59" s="32"/>
       <c r="F59" s="32" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G59" s="33" t="s">
         <v>18</v>
@@ -3809,11 +3809,11 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
       <c r="B60" s="5"/>
       <c r="C60" s="35" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D60" s="32" t="s">
         <v>56</v>
@@ -3829,7 +3829,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="4"/>
       <c r="B61" s="5"/>
       <c r="C61" s="35" t="s">
@@ -3849,7 +3849,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="4"/>
       <c r="B62" s="5"/>
       <c r="C62" s="35" t="s">
@@ -3869,7 +3869,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="4"/>
       <c r="B63" s="5"/>
       <c r="C63" s="35" t="s">
@@ -3889,14 +3889,14 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="4"/>
       <c r="B64" s="5"/>
       <c r="C64" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="D64" s="32" t="s">
         <v>197</v>
-      </c>
-      <c r="D64" s="32" t="s">
-        <v>198</v>
       </c>
       <c r="E64" s="32"/>
       <c r="F64" s="32" t="s">
@@ -3909,11 +3909,11 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="4"/>
       <c r="B65" s="5"/>
       <c r="C65" s="33" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D65" s="32" t="s">
         <v>34</v>
@@ -3929,11 +3929,11 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="4"/>
       <c r="B66" s="5"/>
       <c r="C66" s="33" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D66" s="32" t="s">
         <v>65</v>
@@ -3949,18 +3949,18 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="4"/>
       <c r="B67" s="5"/>
       <c r="C67" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="D67" s="32" t="s">
         <v>201</v>
-      </c>
-      <c r="D67" s="32" t="s">
-        <v>202</v>
       </c>
       <c r="E67" s="32"/>
       <c r="F67" s="33" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>18</v>
@@ -3969,18 +3969,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
       <c r="B68" s="5"/>
       <c r="C68" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="D68" s="32" t="s">
         <v>203</v>
-      </c>
-      <c r="D68" s="32" t="s">
-        <v>204</v>
       </c>
       <c r="E68" s="32"/>
       <c r="F68" s="32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G68" s="6" t="s">
         <v>18</v>
@@ -3989,14 +3989,14 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
       <c r="B69" s="5"/>
       <c r="C69" s="33" t="s">
         <v>40</v>
       </c>
       <c r="D69" s="32" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E69" s="32"/>
       <c r="F69" s="32" t="s">
@@ -4009,14 +4009,14 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
       <c r="B70" s="5"/>
       <c r="C70" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="D70" s="32" t="s">
         <v>207</v>
-      </c>
-      <c r="D70" s="32" t="s">
-        <v>208</v>
       </c>
       <c r="E70" s="32"/>
       <c r="F70" s="32" t="s">
@@ -4029,14 +4029,14 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
       <c r="B71" s="5"/>
       <c r="C71" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="D71" s="32" t="s">
         <v>209</v>
-      </c>
-      <c r="D71" s="32" t="s">
-        <v>210</v>
       </c>
       <c r="E71" s="32"/>
       <c r="F71" s="32" t="s">
@@ -4049,18 +4049,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
       <c r="B72" s="5"/>
       <c r="C72" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="D72" s="32" t="s">
         <v>211</v>
-      </c>
-      <c r="D72" s="32" t="s">
-        <v>212</v>
       </c>
       <c r="E72" s="32"/>
       <c r="F72" s="32" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>18</v>
@@ -4069,18 +4069,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="4"/>
       <c r="B73" s="5"/>
       <c r="C73" s="33" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D73" s="32" t="s">
         <v>43</v>
       </c>
       <c r="E73" s="32"/>
       <c r="F73" s="32" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>18</v>
@@ -4089,18 +4089,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="4"/>
       <c r="B74" s="5"/>
       <c r="C74" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D74" s="32" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E74" s="32"/>
       <c r="F74" s="32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>18</v>
@@ -4109,14 +4109,14 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
       <c r="B75" s="5"/>
       <c r="C75" s="33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D75" s="32" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E75" s="32"/>
       <c r="F75" s="32" t="s">
@@ -4129,18 +4129,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
       <c r="B76" s="5"/>
       <c r="C76" s="33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D76" s="32" t="s">
         <v>25</v>
       </c>
       <c r="E76" s="32"/>
       <c r="F76" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G76" s="6" t="s">
         <v>18</v>
@@ -4149,14 +4149,14 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
       <c r="B77" s="5"/>
       <c r="C77" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="D77" s="32" t="s">
         <v>220</v>
-      </c>
-      <c r="D77" s="32" t="s">
-        <v>221</v>
       </c>
       <c r="E77" s="32"/>
       <c r="F77" s="32" t="s">
@@ -4169,18 +4169,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
       <c r="B78" s="5"/>
       <c r="C78" s="33" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D78" s="32" t="s">
         <v>36</v>
       </c>
       <c r="E78" s="32"/>
       <c r="F78" s="32" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>18</v>
@@ -4189,18 +4189,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
       <c r="B79" s="5"/>
       <c r="C79" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="D79" s="32" t="s">
         <v>224</v>
-      </c>
-      <c r="D79" s="32" t="s">
-        <v>225</v>
       </c>
       <c r="E79" s="32"/>
       <c r="F79" s="32" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G79" s="6" t="s">
         <v>18</v>
@@ -4209,18 +4209,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
       <c r="B80" s="5"/>
       <c r="C80" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="D80" s="32" t="s">
         <v>227</v>
-      </c>
-      <c r="D80" s="32" t="s">
-        <v>228</v>
       </c>
       <c r="E80" s="32"/>
       <c r="F80" s="32" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G80" s="6" t="s">
         <v>18</v>
@@ -4229,18 +4229,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
       <c r="B81" s="5"/>
       <c r="C81" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="D81" s="32" t="s">
         <v>230</v>
-      </c>
-      <c r="D81" s="32" t="s">
-        <v>231</v>
       </c>
       <c r="E81" s="32"/>
       <c r="F81" s="32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G81" s="6" t="s">
         <v>18</v>
@@ -4249,11 +4249,11 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="4"/>
       <c r="B82" s="5"/>
       <c r="C82" s="33" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D82" s="32" t="s">
         <v>35</v>
@@ -4269,14 +4269,14 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="4"/>
       <c r="B83" s="5"/>
       <c r="C83" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="D83" s="32" t="s">
         <v>234</v>
-      </c>
-      <c r="D83" s="32" t="s">
-        <v>235</v>
       </c>
       <c r="E83" s="32"/>
       <c r="F83" s="32" t="s">
@@ -4289,18 +4289,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="4"/>
       <c r="B84" s="5"/>
       <c r="C84" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="D84" s="32" t="s">
         <v>236</v>
-      </c>
-      <c r="D84" s="32" t="s">
-        <v>237</v>
       </c>
       <c r="E84" s="32"/>
       <c r="F84" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G84" s="6" t="s">
         <v>18</v>
@@ -4309,18 +4309,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
       <c r="B85" s="5"/>
       <c r="C85" s="33" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D85" s="32" t="s">
         <v>46</v>
       </c>
       <c r="E85" s="32"/>
       <c r="F85" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G85" s="6" t="s">
         <v>18</v>
@@ -4329,18 +4329,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="4"/>
       <c r="B86" s="5"/>
       <c r="C86" s="33" t="s">
+        <v>238</v>
+      </c>
+      <c r="D86" s="32" t="s">
         <v>239</v>
-      </c>
-      <c r="D86" s="32" t="s">
-        <v>240</v>
       </c>
       <c r="E86" s="32"/>
       <c r="F86" s="32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G86" s="6" t="s">
         <v>18</v>
@@ -4349,18 +4349,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
       <c r="B87" s="5"/>
       <c r="C87" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="D87" s="32" t="s">
         <v>241</v>
-      </c>
-      <c r="D87" s="32" t="s">
-        <v>242</v>
       </c>
       <c r="E87" s="32"/>
       <c r="F87" s="32" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G87" s="6" t="s">
         <v>18</v>
@@ -4369,18 +4369,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
       <c r="B88" s="5"/>
       <c r="C88" s="33" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D88" s="32" t="s">
         <v>44</v>
       </c>
       <c r="E88" s="32"/>
       <c r="F88" s="32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G88" s="6" t="s">
         <v>18</v>
@@ -4389,18 +4389,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
       <c r="B89" s="5"/>
       <c r="C89" s="33" t="s">
+        <v>244</v>
+      </c>
+      <c r="D89" s="32" t="s">
         <v>245</v>
-      </c>
-      <c r="D89" s="32" t="s">
-        <v>246</v>
       </c>
       <c r="E89" s="32"/>
       <c r="F89" s="32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G89" s="6" t="s">
         <v>18</v>
@@ -4409,18 +4409,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="4"/>
       <c r="B90" s="5"/>
       <c r="C90" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="D90" s="32" t="s">
         <v>247</v>
-      </c>
-      <c r="D90" s="32" t="s">
-        <v>248</v>
       </c>
       <c r="E90" s="32"/>
       <c r="F90" s="32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G90" s="6" t="s">
         <v>18</v>
@@ -4429,14 +4429,14 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="4"/>
       <c r="B91" s="5"/>
       <c r="C91" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="D91" s="32" t="s">
         <v>249</v>
-      </c>
-      <c r="D91" s="32" t="s">
-        <v>250</v>
       </c>
       <c r="E91" s="32"/>
       <c r="F91" s="32" t="s">
@@ -4449,18 +4449,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="4"/>
       <c r="B92" s="5"/>
       <c r="C92" s="33" t="s">
+        <v>251</v>
+      </c>
+      <c r="D92" s="32" t="s">
         <v>252</v>
-      </c>
-      <c r="D92" s="32" t="s">
-        <v>253</v>
       </c>
       <c r="E92" s="32"/>
       <c r="F92" s="32" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G92" s="6" t="s">
         <v>18</v>
@@ -4469,18 +4469,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="4"/>
       <c r="B93" s="5"/>
       <c r="C93" s="35" t="s">
+        <v>254</v>
+      </c>
+      <c r="D93" s="32" t="s">
         <v>255</v>
-      </c>
-      <c r="D93" s="32" t="s">
-        <v>256</v>
       </c>
       <c r="E93" s="32"/>
       <c r="F93" s="35" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G93" s="6" t="s">
         <v>18</v>
@@ -4489,18 +4489,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="4"/>
       <c r="B94" s="5"/>
       <c r="C94" s="35" t="s">
+        <v>257</v>
+      </c>
+      <c r="D94" s="32" t="s">
         <v>258</v>
-      </c>
-      <c r="D94" s="32" t="s">
-        <v>259</v>
       </c>
       <c r="E94" s="32"/>
       <c r="F94" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G94" s="6" t="s">
         <v>18</v>
@@ -4509,7 +4509,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="4"/>
       <c r="B95" s="5"/>
       <c r="C95" s="35" t="s">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="E95" s="32"/>
       <c r="F95" s="35" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G95" s="6" t="s">
         <v>18</v>
@@ -4529,18 +4529,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="4"/>
       <c r="B96" s="5"/>
       <c r="C96" s="35" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D96" s="32" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E96" s="32"/>
       <c r="F96" s="35" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G96" s="6" t="s">
         <v>18</v>
@@ -4549,18 +4549,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="4"/>
       <c r="B97" s="5"/>
       <c r="C97" s="33" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D97" s="32" t="s">
         <v>37</v>
       </c>
       <c r="E97" s="32"/>
       <c r="F97" s="35" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G97" s="6" t="s">
         <v>18</v>
@@ -4569,18 +4569,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="4"/>
       <c r="B98" s="5"/>
       <c r="C98" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="D98" s="32" t="s">
         <v>264</v>
-      </c>
-      <c r="D98" s="32" t="s">
-        <v>265</v>
       </c>
       <c r="E98" s="32"/>
       <c r="F98" s="35" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G98" s="6" t="s">
         <v>18</v>
@@ -4589,18 +4589,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="4"/>
       <c r="B99" s="5"/>
       <c r="C99" s="33" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D99" s="32" t="s">
         <v>30</v>
       </c>
       <c r="E99" s="32"/>
       <c r="F99" s="35" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G99" s="6" t="s">
         <v>18</v>
@@ -4609,18 +4609,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="4"/>
       <c r="B100" s="5"/>
       <c r="C100" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="D100" s="32" t="s">
         <v>267</v>
-      </c>
-      <c r="D100" s="32" t="s">
-        <v>268</v>
       </c>
       <c r="E100" s="32"/>
       <c r="F100" s="35" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G100" s="6" t="s">
         <v>18</v>
@@ -4629,18 +4629,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
       <c r="B101" s="5"/>
       <c r="C101" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="D101" s="32" t="s">
         <v>269</v>
-      </c>
-      <c r="D101" s="32" t="s">
-        <v>270</v>
       </c>
       <c r="E101" s="32"/>
       <c r="F101" s="35" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G101" s="6" t="s">
         <v>18</v>
@@ -4649,18 +4649,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="4"/>
       <c r="B102" s="5"/>
       <c r="C102" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="D102" s="32" t="s">
         <v>271</v>
-      </c>
-      <c r="D102" s="32" t="s">
-        <v>272</v>
       </c>
       <c r="E102" s="32"/>
       <c r="F102" s="32" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G102" s="6" t="s">
         <v>18</v>
@@ -4669,18 +4669,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="4"/>
       <c r="B103" s="5"/>
       <c r="C103" s="33" t="s">
+        <v>273</v>
+      </c>
+      <c r="D103" s="32" t="s">
         <v>274</v>
-      </c>
-      <c r="D103" s="32" t="s">
-        <v>275</v>
       </c>
       <c r="E103" s="32"/>
       <c r="F103" s="32" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G103" s="6" t="s">
         <v>18</v>
@@ -4689,18 +4689,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" s="4"/>
       <c r="B104" s="5"/>
       <c r="C104" s="33" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D104" s="32" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E104" s="32"/>
       <c r="F104" s="32" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G104" s="6" t="s">
         <v>18</v>
@@ -4709,18 +4709,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="4"/>
       <c r="B105" s="5"/>
       <c r="C105" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="D105" s="32" t="s">
         <v>277</v>
-      </c>
-      <c r="D105" s="32" t="s">
-        <v>278</v>
       </c>
       <c r="E105" s="32"/>
       <c r="F105" s="32" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G105" s="6" t="s">
         <v>18</v>
@@ -4729,18 +4729,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" s="4"/>
       <c r="B106" s="5"/>
       <c r="C106" s="33" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D106" s="32" t="s">
         <v>32</v>
       </c>
       <c r="E106" s="32"/>
       <c r="F106" s="32" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G106" s="6" t="s">
         <v>18</v>
@@ -4749,18 +4749,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" s="4"/>
       <c r="B107" s="5"/>
       <c r="C107" s="33" t="s">
+        <v>280</v>
+      </c>
+      <c r="D107" s="32" t="s">
         <v>281</v>
-      </c>
-      <c r="D107" s="32" t="s">
-        <v>282</v>
       </c>
       <c r="E107" s="32"/>
       <c r="F107" s="32" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G107" s="6" t="s">
         <v>18</v>
@@ -4769,18 +4769,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" s="4"/>
       <c r="B108" s="5"/>
       <c r="C108" s="33" t="s">
+        <v>282</v>
+      </c>
+      <c r="D108" s="32" t="s">
         <v>283</v>
-      </c>
-      <c r="D108" s="32" t="s">
-        <v>284</v>
       </c>
       <c r="E108" s="32"/>
       <c r="F108" s="32" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G108" s="6" t="s">
         <v>18</v>
@@ -4789,18 +4789,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" s="4"/>
       <c r="B109" s="5"/>
       <c r="C109" s="33" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D109" s="32" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E109" s="32"/>
       <c r="F109" s="32" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G109" s="6" t="s">
         <v>18</v>
@@ -4809,18 +4809,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" s="4"/>
       <c r="B110" s="5"/>
       <c r="C110" s="33" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D110" s="32" t="s">
         <v>79</v>
       </c>
       <c r="E110" s="32"/>
       <c r="F110" s="32" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G110" s="6" t="s">
         <v>18</v>
@@ -4829,18 +4829,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="4"/>
       <c r="B111" s="5"/>
       <c r="C111" s="33" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D111" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E111" s="32"/>
       <c r="F111" s="32" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G111" s="6" t="s">
         <v>18</v>
@@ -4849,18 +4849,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" s="4"/>
       <c r="B112" s="5"/>
       <c r="C112" s="33" t="s">
         <v>40</v>
       </c>
       <c r="D112" s="32" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E112" s="32"/>
       <c r="F112" s="32" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G112" s="6" t="s">
         <v>18</v>
@@ -4869,18 +4869,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" s="4"/>
       <c r="B113" s="5"/>
       <c r="C113" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="D113" s="32" t="s">
         <v>293</v>
-      </c>
-      <c r="D113" s="32" t="s">
-        <v>294</v>
       </c>
       <c r="E113" s="32"/>
       <c r="F113" s="32" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G113" s="6" t="s">
         <v>18</v>
@@ -4889,18 +4889,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="4"/>
       <c r="B114" s="5"/>
       <c r="C114" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="D114" s="32" t="s">
         <v>295</v>
-      </c>
-      <c r="D114" s="32" t="s">
-        <v>296</v>
       </c>
       <c r="E114" s="32"/>
       <c r="F114" s="32" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G114" s="6" t="s">
         <v>18</v>
@@ -4909,18 +4909,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A115" s="4"/>
       <c r="B115" s="5"/>
       <c r="C115" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="D115" s="32" t="s">
         <v>298</v>
-      </c>
-      <c r="D115" s="32" t="s">
-        <v>299</v>
       </c>
       <c r="E115" s="32"/>
       <c r="F115" s="32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G115" s="6" t="s">
         <v>18</v>
@@ -4929,18 +4929,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A116" s="4"/>
       <c r="B116" s="5"/>
       <c r="C116" s="33" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D116" s="32" t="s">
         <v>43</v>
       </c>
       <c r="E116" s="32"/>
       <c r="F116" s="32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G116" s="6" t="s">
         <v>18</v>
@@ -4949,18 +4949,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" s="4"/>
       <c r="B117" s="5"/>
       <c r="C117" s="33" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D117" s="32" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E117" s="32"/>
       <c r="F117" s="32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G117" s="6" t="s">
         <v>18</v>
@@ -4969,18 +4969,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" s="4"/>
       <c r="B118" s="5"/>
       <c r="C118" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="D118" s="32" t="s">
         <v>302</v>
-      </c>
-      <c r="D118" s="32" t="s">
-        <v>303</v>
       </c>
       <c r="E118" s="32"/>
       <c r="F118" s="32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G118" s="6" t="s">
         <v>18</v>
@@ -4989,18 +4989,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A119" s="4"/>
       <c r="B119" s="5"/>
       <c r="C119" s="33" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D119" s="32" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E119" s="32"/>
       <c r="F119" s="32" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G119" s="6" t="s">
         <v>18</v>
@@ -5009,18 +5009,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A120" s="4"/>
       <c r="B120" s="5"/>
       <c r="C120" s="33" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D120" s="32" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E120" s="32"/>
       <c r="F120" s="32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G120" s="6" t="s">
         <v>18</v>
@@ -5029,18 +5029,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A121" s="4"/>
       <c r="B121" s="5"/>
       <c r="C121" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="D121" s="32" t="s">
         <v>307</v>
-      </c>
-      <c r="D121" s="32" t="s">
-        <v>308</v>
       </c>
       <c r="E121" s="32"/>
       <c r="F121" s="32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G121" s="6" t="s">
         <v>18</v>
@@ -5049,14 +5049,14 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A122" s="4"/>
       <c r="B122" s="5"/>
       <c r="C122" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="D122" s="32" t="s">
         <v>309</v>
-      </c>
-      <c r="D122" s="32" t="s">
-        <v>310</v>
       </c>
       <c r="E122" s="32"/>
       <c r="F122" s="32" t="s">
@@ -5069,18 +5069,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A123" s="4"/>
       <c r="B123" s="5"/>
       <c r="C123" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="D123" s="32" t="s">
         <v>311</v>
-      </c>
-      <c r="D123" s="32" t="s">
-        <v>312</v>
       </c>
       <c r="E123" s="32"/>
       <c r="F123" s="32" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G123" s="6" t="s">
         <v>18</v>
@@ -5089,18 +5089,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A124" s="4"/>
       <c r="B124" s="5"/>
       <c r="C124" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="D124" s="32" t="s">
         <v>314</v>
-      </c>
-      <c r="D124" s="32" t="s">
-        <v>315</v>
       </c>
       <c r="E124" s="32"/>
       <c r="F124" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G124" s="6" t="s">
         <v>18</v>
@@ -5109,18 +5109,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A125" s="4"/>
       <c r="B125" s="5"/>
       <c r="C125" s="33" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D125" s="32" t="s">
         <v>32</v>
       </c>
       <c r="E125" s="32"/>
       <c r="F125" s="32" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G125" s="6" t="s">
         <v>18</v>
@@ -5129,18 +5129,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A126" s="4"/>
       <c r="B126" s="5"/>
       <c r="C126" s="33" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D126" s="32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E126" s="32"/>
       <c r="F126" s="32" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G126" s="6" t="s">
         <v>18</v>
@@ -5149,14 +5149,14 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A127" s="4"/>
       <c r="B127" s="5"/>
       <c r="C127" s="33" t="s">
         <v>59</v>
       </c>
       <c r="D127" s="32" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E127" s="32"/>
       <c r="F127" s="32" t="s">
@@ -5169,18 +5169,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A128" s="4"/>
       <c r="B128" s="5"/>
       <c r="C128" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="D128" s="32" t="s">
         <v>320</v>
-      </c>
-      <c r="D128" s="32" t="s">
-        <v>321</v>
       </c>
       <c r="E128" s="32"/>
       <c r="F128" s="32" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G128" s="6" t="s">
         <v>18</v>
@@ -5189,18 +5189,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A129" s="4"/>
       <c r="B129" s="5"/>
       <c r="C129" s="33" t="s">
+        <v>323</v>
+      </c>
+      <c r="D129" s="32" t="s">
         <v>324</v>
-      </c>
-      <c r="D129" s="32" t="s">
-        <v>325</v>
       </c>
       <c r="E129" s="32"/>
       <c r="F129" s="32" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G129" s="6" t="s">
         <v>18</v>
@@ -5209,18 +5209,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A130" s="4"/>
       <c r="B130" s="5"/>
       <c r="C130" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="D130" s="32" t="s">
         <v>327</v>
-      </c>
-      <c r="D130" s="32" t="s">
-        <v>328</v>
       </c>
       <c r="E130" s="32"/>
       <c r="F130" s="32" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G130" s="6" t="s">
         <v>18</v>
@@ -5229,18 +5229,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A131" s="4"/>
       <c r="B131" s="5"/>
       <c r="C131" s="33" t="s">
+        <v>328</v>
+      </c>
+      <c r="D131" s="32" t="s">
         <v>329</v>
-      </c>
-      <c r="D131" s="32" t="s">
-        <v>330</v>
       </c>
       <c r="E131" s="32"/>
       <c r="F131" s="32" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G131" s="6" t="s">
         <v>18</v>
@@ -5249,18 +5249,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A132" s="4"/>
       <c r="B132" s="5"/>
       <c r="C132" s="33" t="s">
+        <v>330</v>
+      </c>
+      <c r="D132" s="32" t="s">
         <v>331</v>
-      </c>
-      <c r="D132" s="32" t="s">
-        <v>332</v>
       </c>
       <c r="E132" s="32"/>
       <c r="F132" s="32" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G132" s="6" t="s">
         <v>18</v>
@@ -5269,18 +5269,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A133" s="4"/>
       <c r="B133" s="5"/>
       <c r="C133" s="33" t="s">
+        <v>333</v>
+      </c>
+      <c r="D133" s="32" t="s">
         <v>334</v>
-      </c>
-      <c r="D133" s="32" t="s">
-        <v>335</v>
       </c>
       <c r="E133" s="32"/>
       <c r="F133" s="32" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G133" s="6" t="s">
         <v>18</v>
@@ -5289,18 +5289,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A134" s="4"/>
       <c r="B134" s="5"/>
       <c r="C134" s="33" t="s">
+        <v>336</v>
+      </c>
+      <c r="D134" s="32" t="s">
         <v>337</v>
-      </c>
-      <c r="D134" s="32" t="s">
-        <v>338</v>
       </c>
       <c r="E134" s="32"/>
       <c r="F134" s="32" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G134" s="6" t="s">
         <v>18</v>
@@ -5309,7 +5309,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A135" s="4"/>
       <c r="B135" s="5"/>
       <c r="C135" s="33" t="s">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="E135" s="32"/>
       <c r="F135" s="32" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G135" s="6" t="s">
         <v>18</v>
@@ -5329,18 +5329,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A136" s="4"/>
       <c r="B136" s="5"/>
       <c r="C136" s="33" t="s">
+        <v>339</v>
+      </c>
+      <c r="D136" s="32" t="s">
         <v>340</v>
-      </c>
-      <c r="D136" s="32" t="s">
-        <v>341</v>
       </c>
       <c r="E136" s="32"/>
       <c r="F136" s="32" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G136" s="6" t="s">
         <v>18</v>
@@ -5349,18 +5349,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A137" s="4"/>
       <c r="B137" s="5"/>
       <c r="C137" s="33" t="s">
         <v>22</v>
       </c>
       <c r="D137" s="32" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E137" s="32"/>
       <c r="F137" s="32" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G137" s="6" t="s">
         <v>18</v>
@@ -5369,18 +5369,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A138" s="4"/>
       <c r="B138" s="5"/>
       <c r="C138" s="33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D138" s="32" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E138" s="32"/>
       <c r="F138" s="32" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G138" s="6" t="s">
         <v>18</v>
@@ -5389,18 +5389,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A139" s="4"/>
       <c r="B139" s="5"/>
       <c r="C139" s="33" t="s">
+        <v>345</v>
+      </c>
+      <c r="D139" s="32" t="s">
         <v>346</v>
-      </c>
-      <c r="D139" s="32" t="s">
-        <v>347</v>
       </c>
       <c r="E139" s="32"/>
       <c r="F139" s="32" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G139" s="6" t="s">
         <v>18</v>
@@ -5409,18 +5409,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A140" s="4"/>
       <c r="B140" s="5"/>
       <c r="C140" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="D140" s="32" t="s">
         <v>349</v>
-      </c>
-      <c r="D140" s="32" t="s">
-        <v>350</v>
       </c>
       <c r="E140" s="32"/>
       <c r="F140" s="32" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G140" s="6" t="s">
         <v>18</v>
@@ -5429,14 +5429,14 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A141" s="4"/>
       <c r="B141" s="5"/>
       <c r="C141" s="33" t="s">
+        <v>351</v>
+      </c>
+      <c r="D141" s="32" t="s">
         <v>352</v>
-      </c>
-      <c r="D141" s="32" t="s">
-        <v>353</v>
       </c>
       <c r="E141" s="32"/>
       <c r="F141" s="32" t="s">
@@ -5449,18 +5449,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A142" s="4"/>
       <c r="B142" s="5"/>
       <c r="C142" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="D142" s="32" t="s">
         <v>354</v>
-      </c>
-      <c r="D142" s="32" t="s">
-        <v>355</v>
       </c>
       <c r="E142" s="32"/>
       <c r="F142" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G142" s="6" t="s">
         <v>18</v>
@@ -5469,18 +5469,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A143" s="4"/>
       <c r="B143" s="5"/>
       <c r="C143" s="33" t="s">
+        <v>355</v>
+      </c>
+      <c r="D143" s="32" t="s">
         <v>356</v>
-      </c>
-      <c r="D143" s="32" t="s">
-        <v>357</v>
       </c>
       <c r="E143" s="32"/>
       <c r="F143" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G143" s="6" t="s">
         <v>18</v>
@@ -5489,18 +5489,18 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A144" s="4"/>
       <c r="B144" s="5"/>
       <c r="C144" s="33" t="s">
+        <v>357</v>
+      </c>
+      <c r="D144" s="32" t="s">
         <v>358</v>
-      </c>
-      <c r="D144" s="32" t="s">
-        <v>359</v>
       </c>
       <c r="E144" s="32"/>
       <c r="F144" s="32" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G144" s="6" t="s">
         <v>18</v>
@@ -5509,18 +5509,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A145" s="4"/>
       <c r="B145" s="5"/>
       <c r="C145" s="33" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D145" s="32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E145" s="32"/>
       <c r="F145" s="32" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G145" s="6" t="s">
         <v>18</v>
@@ -5529,18 +5529,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A146" s="4"/>
       <c r="B146" s="5"/>
       <c r="C146" s="33" t="s">
+        <v>362</v>
+      </c>
+      <c r="D146" s="32" t="s">
         <v>363</v>
-      </c>
-      <c r="D146" s="32" t="s">
-        <v>364</v>
       </c>
       <c r="E146" s="32"/>
       <c r="F146" s="32" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G146" s="6" t="s">
         <v>18</v>
@@ -5549,18 +5549,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A147" s="4"/>
       <c r="B147" s="5"/>
       <c r="C147" s="33" t="s">
+        <v>364</v>
+      </c>
+      <c r="D147" s="32" t="s">
         <v>365</v>
-      </c>
-      <c r="D147" s="32" t="s">
-        <v>366</v>
       </c>
       <c r="E147" s="32"/>
       <c r="F147" s="32" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G147" s="6" t="s">
         <v>18</v>
@@ -5569,18 +5569,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A148" s="4"/>
       <c r="B148" s="5"/>
       <c r="C148" s="33" t="s">
+        <v>367</v>
+      </c>
+      <c r="D148" s="32" t="s">
         <v>368</v>
-      </c>
-      <c r="D148" s="32" t="s">
-        <v>369</v>
       </c>
       <c r="E148" s="32"/>
       <c r="F148" s="32" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G148" s="6" t="s">
         <v>18</v>
@@ -5589,18 +5589,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A149" s="4"/>
       <c r="B149" s="5"/>
       <c r="C149" s="33" t="s">
+        <v>370</v>
+      </c>
+      <c r="D149" s="32" t="s">
         <v>371</v>
-      </c>
-      <c r="D149" s="32" t="s">
-        <v>372</v>
       </c>
       <c r="E149" s="32"/>
       <c r="F149" s="32" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G149" s="6" t="s">
         <v>18</v>
@@ -5609,18 +5609,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A150" s="4"/>
       <c r="B150" s="5"/>
       <c r="C150" s="33" t="s">
         <v>51</v>
       </c>
       <c r="D150" s="32" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E150" s="32"/>
       <c r="F150" s="32" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G150" s="6" t="s">
         <v>18</v>
@@ -5629,18 +5629,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A151" s="4"/>
       <c r="B151" s="5"/>
       <c r="C151" s="33" t="s">
+        <v>373</v>
+      </c>
+      <c r="D151" s="32" t="s">
         <v>374</v>
-      </c>
-      <c r="D151" s="32" t="s">
-        <v>375</v>
       </c>
       <c r="E151" s="32"/>
       <c r="F151" s="32" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G151" s="6" t="s">
         <v>18</v>
@@ -5649,18 +5649,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A152" s="4"/>
       <c r="B152" s="5"/>
       <c r="C152" s="33" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D152" s="32" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E152" s="32"/>
       <c r="F152" s="32" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G152" s="6" t="s">
         <v>18</v>
@@ -5669,18 +5669,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A153" s="4"/>
       <c r="B153" s="5"/>
       <c r="C153" s="33" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D153" s="32" t="s">
         <v>37</v>
       </c>
       <c r="E153" s="32"/>
       <c r="F153" s="32" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G153" s="6" t="s">
         <v>18</v>
@@ -5689,18 +5689,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A154" s="4"/>
       <c r="B154" s="5"/>
       <c r="C154" s="33" t="s">
+        <v>378</v>
+      </c>
+      <c r="D154" s="32" t="s">
         <v>379</v>
-      </c>
-      <c r="D154" s="32" t="s">
-        <v>380</v>
       </c>
       <c r="E154" s="32"/>
       <c r="F154" s="32" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G154" s="6" t="s">
         <v>18</v>
@@ -5709,18 +5709,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A155" s="4"/>
       <c r="B155" s="5"/>
       <c r="C155" s="33" t="s">
         <v>50</v>
       </c>
       <c r="D155" s="32" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E155" s="32"/>
       <c r="F155" s="32" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G155" s="6" t="s">
         <v>18</v>
@@ -5729,18 +5729,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A156" s="4"/>
       <c r="B156" s="5"/>
       <c r="C156" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="D156" s="32" t="s">
         <v>382</v>
-      </c>
-      <c r="D156" s="32" t="s">
-        <v>383</v>
       </c>
       <c r="E156" s="32"/>
       <c r="F156" s="32" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G156" s="6" t="s">
         <v>18</v>
@@ -5749,18 +5749,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A157" s="4"/>
       <c r="B157" s="5"/>
       <c r="C157" s="33" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D157" s="32" t="s">
         <v>30</v>
       </c>
       <c r="E157" s="32"/>
       <c r="F157" s="32" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G157" s="6" t="s">
         <v>18</v>
@@ -5769,18 +5769,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="4"/>
       <c r="B158" s="5"/>
       <c r="C158" s="33" t="s">
+        <v>385</v>
+      </c>
+      <c r="D158" s="32" t="s">
         <v>386</v>
-      </c>
-      <c r="D158" s="32" t="s">
-        <v>387</v>
       </c>
       <c r="E158" s="32"/>
       <c r="F158" s="32" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G158" s="6" t="s">
         <v>18</v>
@@ -5789,18 +5789,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A159" s="4"/>
       <c r="B159" s="5"/>
       <c r="C159" s="33" t="s">
+        <v>388</v>
+      </c>
+      <c r="D159" s="32" t="s">
         <v>389</v>
-      </c>
-      <c r="D159" s="32" t="s">
-        <v>390</v>
       </c>
       <c r="E159" s="32"/>
       <c r="F159" s="32" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G159" s="6" t="s">
         <v>18</v>
@@ -5809,18 +5809,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A160" s="4"/>
       <c r="B160" s="5"/>
       <c r="C160" s="33" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D160" s="32" t="s">
         <v>64</v>
       </c>
       <c r="E160" s="32"/>
       <c r="F160" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G160" s="6" t="s">
         <v>18</v>
@@ -5829,18 +5829,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A161" s="4"/>
       <c r="B161" s="5"/>
       <c r="C161" s="33" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D161" s="32" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E161" s="32"/>
       <c r="F161" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G161" s="6" t="s">
         <v>18</v>
@@ -5849,18 +5849,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A162" s="4"/>
       <c r="B162" s="5"/>
       <c r="C162" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="D162" s="32" t="s">
         <v>395</v>
-      </c>
-      <c r="D162" s="32" t="s">
-        <v>396</v>
       </c>
       <c r="E162" s="32"/>
       <c r="F162" s="32" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G162" s="6" t="s">
         <v>18</v>
@@ -5869,18 +5869,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A163" s="4"/>
       <c r="B163" s="5"/>
       <c r="C163" s="33" t="s">
+        <v>396</v>
+      </c>
+      <c r="D163" s="32" t="s">
         <v>397</v>
-      </c>
-      <c r="D163" s="32" t="s">
-        <v>398</v>
       </c>
       <c r="E163" s="32"/>
       <c r="F163" s="32" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G163" s="6" t="s">
         <v>18</v>
@@ -5889,18 +5889,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A164" s="4"/>
       <c r="B164" s="5"/>
       <c r="C164" s="33" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D164" s="32" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E164" s="32"/>
       <c r="F164" s="32" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G164" s="6" t="s">
         <v>18</v>
@@ -5909,18 +5909,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A165" s="4"/>
       <c r="B165" s="5"/>
       <c r="C165" s="33" t="s">
+        <v>401</v>
+      </c>
+      <c r="D165" s="32" t="s">
         <v>402</v>
-      </c>
-      <c r="D165" s="32" t="s">
-        <v>403</v>
       </c>
       <c r="E165" s="32"/>
       <c r="F165" s="32" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G165" s="6" t="s">
         <v>18</v>
@@ -5929,18 +5929,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A166" s="4"/>
       <c r="B166" s="5"/>
       <c r="C166" s="33" t="s">
+        <v>403</v>
+      </c>
+      <c r="D166" s="32" t="s">
         <v>404</v>
-      </c>
-      <c r="D166" s="32" t="s">
-        <v>405</v>
       </c>
       <c r="E166" s="32"/>
       <c r="F166" s="32" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G166" s="6" t="s">
         <v>18</v>
@@ -5949,18 +5949,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A167" s="4"/>
       <c r="B167" s="5"/>
       <c r="C167" s="33" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D167" s="32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E167" s="32"/>
       <c r="F167" s="32" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G167" s="6" t="s">
         <v>18</v>
@@ -5969,18 +5969,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A168" s="4"/>
       <c r="B168" s="5"/>
       <c r="C168" s="33" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D168" s="32" t="s">
         <v>54</v>
       </c>
       <c r="E168" s="32"/>
       <c r="F168" s="32" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G168" s="6" t="s">
         <v>18</v>
@@ -5989,18 +5989,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A169" s="4"/>
       <c r="B169" s="5"/>
       <c r="C169" s="33" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D169" s="32" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E169" s="32"/>
       <c r="F169" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G169" s="6" t="s">
         <v>18</v>
@@ -6009,18 +6009,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A170" s="4"/>
       <c r="B170" s="5"/>
       <c r="C170" s="33" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D170" s="32" t="s">
         <v>41</v>
       </c>
       <c r="E170" s="32"/>
       <c r="F170" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G170" s="6" t="s">
         <v>18</v>
@@ -6029,18 +6029,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A171" s="4"/>
       <c r="B171" s="5"/>
       <c r="C171" s="33" t="s">
+        <v>412</v>
+      </c>
+      <c r="D171" s="32" t="s">
         <v>413</v>
-      </c>
-      <c r="D171" s="32" t="s">
-        <v>414</v>
       </c>
       <c r="E171" s="32"/>
       <c r="F171" s="32" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G171" s="6" t="s">
         <v>18</v>
@@ -6049,18 +6049,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A172" s="4"/>
       <c r="B172" s="5"/>
       <c r="C172" s="33" t="s">
+        <v>415</v>
+      </c>
+      <c r="D172" s="32" t="s">
         <v>416</v>
-      </c>
-      <c r="D172" s="32" t="s">
-        <v>417</v>
       </c>
       <c r="E172" s="32"/>
       <c r="F172" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G172" s="6" t="s">
         <v>18</v>
@@ -6069,18 +6069,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A173" s="4"/>
       <c r="B173" s="5"/>
       <c r="C173" s="33" t="s">
+        <v>417</v>
+      </c>
+      <c r="D173" s="32" t="s">
         <v>418</v>
-      </c>
-      <c r="D173" s="32" t="s">
-        <v>419</v>
       </c>
       <c r="E173" s="32"/>
       <c r="F173" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G173" s="6" t="s">
         <v>18</v>
@@ -6089,18 +6089,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A174" s="4"/>
       <c r="B174" s="5"/>
       <c r="C174" s="33" t="s">
+        <v>419</v>
+      </c>
+      <c r="D174" s="32" t="s">
         <v>420</v>
-      </c>
-      <c r="D174" s="32" t="s">
-        <v>421</v>
       </c>
       <c r="E174" s="32"/>
       <c r="F174" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G174" s="6" t="s">
         <v>18</v>
@@ -6109,18 +6109,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A175" s="4"/>
       <c r="B175" s="5"/>
       <c r="C175" s="33" t="s">
+        <v>421</v>
+      </c>
+      <c r="D175" s="32" t="s">
         <v>422</v>
-      </c>
-      <c r="D175" s="32" t="s">
-        <v>423</v>
       </c>
       <c r="E175" s="32"/>
       <c r="F175" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G175" s="6" t="s">
         <v>18</v>
@@ -6129,18 +6129,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A176" s="4"/>
       <c r="B176" s="5"/>
       <c r="C176" s="33" t="s">
+        <v>423</v>
+      </c>
+      <c r="D176" s="32" t="s">
         <v>424</v>
-      </c>
-      <c r="D176" s="32" t="s">
-        <v>425</v>
       </c>
       <c r="E176" s="32"/>
       <c r="F176" s="32" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G176" s="6" t="s">
         <v>18</v>
@@ -6149,18 +6149,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A177" s="4"/>
       <c r="B177" s="5"/>
       <c r="C177" s="33" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D177" s="32" t="s">
         <v>63</v>
       </c>
       <c r="E177" s="32"/>
       <c r="F177" s="32" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G177" s="6" t="s">
         <v>18</v>
@@ -6169,18 +6169,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A178" s="4"/>
       <c r="B178" s="5"/>
       <c r="C178" s="33" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D178" s="32" t="s">
         <v>42</v>
       </c>
       <c r="E178" s="32"/>
       <c r="F178" s="32" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G178" s="6" t="s">
         <v>18</v>
@@ -6189,7 +6189,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A179" s="4"/>
       <c r="B179" s="5"/>
       <c r="C179" s="33" t="s">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="E179" s="32"/>
       <c r="F179" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G179" s="6" t="s">
         <v>18</v>
@@ -6209,18 +6209,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A180" s="4"/>
       <c r="B180" s="5"/>
       <c r="C180" s="33" t="s">
+        <v>428</v>
+      </c>
+      <c r="D180" s="32" t="s">
         <v>429</v>
-      </c>
-      <c r="D180" s="32" t="s">
-        <v>430</v>
       </c>
       <c r="E180" s="32"/>
       <c r="F180" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G180" s="6" t="s">
         <v>18</v>
@@ -6229,18 +6229,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A181" s="4"/>
       <c r="B181" s="5"/>
       <c r="C181" s="33" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D181" s="32" t="s">
         <v>44</v>
       </c>
       <c r="E181" s="32"/>
       <c r="F181" s="32" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G181" s="6" t="s">
         <v>18</v>
@@ -6249,18 +6249,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A182" s="4"/>
       <c r="B182" s="5"/>
       <c r="C182" s="33" t="s">
+        <v>433</v>
+      </c>
+      <c r="D182" s="32" t="s">
         <v>434</v>
-      </c>
-      <c r="D182" s="32" t="s">
-        <v>435</v>
       </c>
       <c r="E182" s="32"/>
       <c r="F182" s="32" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G182" s="6" t="s">
         <v>18</v>
@@ -6269,18 +6269,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A183" s="4"/>
       <c r="B183" s="5"/>
       <c r="C183" s="33" t="s">
+        <v>435</v>
+      </c>
+      <c r="D183" s="32" t="s">
         <v>436</v>
-      </c>
-      <c r="D183" s="32" t="s">
-        <v>437</v>
       </c>
       <c r="E183" s="32"/>
       <c r="F183" s="32" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G183" s="6" t="s">
         <v>18</v>
@@ -6289,18 +6289,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A184" s="4"/>
       <c r="B184" s="5"/>
       <c r="C184" s="33" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D184" s="32" t="s">
         <v>27</v>
       </c>
       <c r="E184" s="32"/>
       <c r="F184" s="32" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G184" s="6" t="s">
         <v>18</v>
@@ -6309,18 +6309,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A185" s="4"/>
       <c r="B185" s="5"/>
       <c r="C185" s="33" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D185" s="32" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E185" s="32"/>
       <c r="F185" s="32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G185" s="6" t="s">
         <v>18</v>
@@ -6329,18 +6329,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A186" s="4"/>
       <c r="B186" s="5"/>
       <c r="C186" s="33" t="s">
+        <v>441</v>
+      </c>
+      <c r="D186" s="32" t="s">
         <v>442</v>
-      </c>
-      <c r="D186" s="32" t="s">
-        <v>443</v>
       </c>
       <c r="E186" s="32"/>
       <c r="F186" s="32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G186" s="6" t="s">
         <v>18</v>
@@ -6349,18 +6349,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A187" s="4"/>
       <c r="B187" s="5"/>
       <c r="C187" s="33" t="s">
+        <v>443</v>
+      </c>
+      <c r="D187" s="32" t="s">
         <v>444</v>
-      </c>
-      <c r="D187" s="32" t="s">
-        <v>445</v>
       </c>
       <c r="E187" s="32"/>
       <c r="F187" s="32" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G187" s="6" t="s">
         <v>18</v>
@@ -6369,18 +6369,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A188" s="4"/>
       <c r="B188" s="5"/>
       <c r="C188" s="33" t="s">
+        <v>446</v>
+      </c>
+      <c r="D188" s="32" t="s">
         <v>447</v>
-      </c>
-      <c r="D188" s="32" t="s">
-        <v>448</v>
       </c>
       <c r="E188" s="32"/>
       <c r="F188" s="32" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G188" s="6" t="s">
         <v>18</v>
@@ -6389,18 +6389,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A189" s="4"/>
       <c r="B189" s="5"/>
       <c r="C189" s="33" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D189" s="32" t="s">
         <v>55</v>
       </c>
       <c r="E189" s="32"/>
       <c r="F189" s="32" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G189" s="6" t="s">
         <v>18</v>
@@ -6409,18 +6409,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A190" s="4"/>
       <c r="B190" s="5"/>
       <c r="C190" s="33" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D190" s="32" t="s">
         <v>23</v>
       </c>
       <c r="E190" s="32"/>
       <c r="F190" s="32" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G190" s="6" t="s">
         <v>18</v>
@@ -6429,18 +6429,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A191" s="4"/>
       <c r="B191" s="5"/>
       <c r="C191" s="33" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D191" s="32" t="s">
         <v>49</v>
       </c>
       <c r="E191" s="32"/>
       <c r="F191" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G191" s="6" t="s">
         <v>20</v>
@@ -6449,38 +6449,38 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A192" s="4"/>
       <c r="B192" s="5"/>
       <c r="C192" s="33" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D192" s="32" t="s">
         <v>41</v>
       </c>
       <c r="E192" s="32"/>
       <c r="F192" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H192" s="7">
         <v>2022</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A193" s="4"/>
       <c r="B193" s="5"/>
       <c r="C193" s="33" t="s">
+        <v>455</v>
+      </c>
+      <c r="D193" s="32" t="s">
         <v>456</v>
-      </c>
-      <c r="D193" s="32" t="s">
-        <v>457</v>
       </c>
       <c r="E193" s="32"/>
       <c r="F193" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G193" s="6" t="s">
         <v>20</v>
@@ -6489,18 +6489,18 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A194" s="4"/>
       <c r="B194" s="5"/>
       <c r="C194" s="33" t="s">
+        <v>457</v>
+      </c>
+      <c r="D194" s="32" t="s">
         <v>458</v>
-      </c>
-      <c r="D194" s="32" t="s">
-        <v>459</v>
       </c>
       <c r="E194" s="32"/>
       <c r="F194" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G194" s="6" t="s">
         <v>20</v>
@@ -6509,18 +6509,18 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A195" s="4"/>
       <c r="B195" s="5"/>
       <c r="C195" s="33" t="s">
+        <v>459</v>
+      </c>
+      <c r="D195" s="32" t="s">
         <v>460</v>
-      </c>
-      <c r="D195" s="32" t="s">
-        <v>461</v>
       </c>
       <c r="E195" s="32"/>
       <c r="F195" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G195" s="6" t="s">
         <v>20</v>
@@ -6529,18 +6529,18 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A196" s="4"/>
       <c r="B196" s="5"/>
       <c r="C196" s="33" t="s">
+        <v>461</v>
+      </c>
+      <c r="D196" s="32" t="s">
         <v>462</v>
-      </c>
-      <c r="D196" s="32" t="s">
-        <v>463</v>
       </c>
       <c r="E196" s="32"/>
       <c r="F196" s="32" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G196" s="6" t="s">
         <v>20</v>
@@ -6549,58 +6549,58 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A197" s="4"/>
       <c r="B197" s="5"/>
       <c r="C197" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="D197" s="32" t="s">
         <v>465</v>
-      </c>
-      <c r="D197" s="32" t="s">
-        <v>466</v>
       </c>
       <c r="E197" s="32"/>
       <c r="F197" s="32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G197" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H197" s="7">
         <v>2022</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A198" s="4"/>
       <c r="B198" s="5"/>
       <c r="C198" s="33" t="s">
+        <v>466</v>
+      </c>
+      <c r="D198" s="32" t="s">
         <v>467</v>
-      </c>
-      <c r="D198" s="32" t="s">
-        <v>468</v>
       </c>
       <c r="E198" s="32"/>
       <c r="F198" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H198" s="7">
         <v>2022</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A199" s="4"/>
       <c r="B199" s="5"/>
       <c r="C199" s="33" t="s">
+        <v>468</v>
+      </c>
+      <c r="D199" s="32" t="s">
         <v>469</v>
-      </c>
-      <c r="D199" s="32" t="s">
-        <v>470</v>
       </c>
       <c r="E199" s="32"/>
       <c r="F199" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G199" s="6" t="s">
         <v>20</v>
@@ -6609,58 +6609,58 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A200" s="4"/>
       <c r="B200" s="5"/>
       <c r="C200" s="33" t="s">
+        <v>470</v>
+      </c>
+      <c r="D200" s="32" t="s">
         <v>471</v>
-      </c>
-      <c r="D200" s="32" t="s">
-        <v>472</v>
       </c>
       <c r="E200" s="32"/>
       <c r="F200" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H200" s="7">
         <v>2022</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A201" s="4"/>
       <c r="B201" s="5"/>
       <c r="C201" s="33" t="s">
+        <v>472</v>
+      </c>
+      <c r="D201" s="32" t="s">
         <v>473</v>
-      </c>
-      <c r="D201" s="32" t="s">
-        <v>474</v>
       </c>
       <c r="E201" s="32"/>
       <c r="F201" s="32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G201" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H201" s="7">
         <v>2022</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A202" s="4"/>
       <c r="B202" s="5"/>
       <c r="C202" s="33" t="s">
+        <v>474</v>
+      </c>
+      <c r="D202" s="32" t="s">
         <v>475</v>
-      </c>
-      <c r="D202" s="32" t="s">
-        <v>476</v>
       </c>
       <c r="E202" s="32"/>
       <c r="F202" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G202" s="6" t="s">
         <v>20</v>
@@ -6669,18 +6669,18 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A203" s="4"/>
       <c r="B203" s="5"/>
       <c r="C203" s="33" t="s">
+        <v>476</v>
+      </c>
+      <c r="D203" s="32" t="s">
         <v>477</v>
-      </c>
-      <c r="D203" s="32" t="s">
-        <v>478</v>
       </c>
       <c r="E203" s="32"/>
       <c r="F203" s="32" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G203" s="6" t="s">
         <v>18</v>
@@ -6689,14 +6689,14 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A204" s="4"/>
       <c r="B204" s="5"/>
       <c r="C204" s="33" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D204" s="32" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E204" s="32"/>
       <c r="F204" s="32" t="s">
@@ -6709,14 +6709,14 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A205" s="4"/>
       <c r="B205" s="5"/>
       <c r="C205" s="33" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D205" s="32" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E205" s="32"/>
       <c r="F205" s="32" t="s">
@@ -6729,14 +6729,14 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A206" s="4"/>
       <c r="B206" s="5"/>
       <c r="C206" s="33" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D206" s="32" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E206" s="32"/>
       <c r="F206" s="32" t="s">
@@ -6749,14 +6749,14 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A207" s="4"/>
       <c r="B207" s="5"/>
       <c r="C207" s="33" t="s">
         <v>74</v>
       </c>
       <c r="D207" s="32" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E207" s="32"/>
       <c r="F207" s="32" t="s">
@@ -6769,38 +6769,38 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A208" s="4"/>
       <c r="B208" s="5"/>
       <c r="C208" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D208" s="32" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E208" s="32"/>
       <c r="F208" s="32" t="s">
         <v>24</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="H208" s="7">
         <v>2026</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A209" s="4"/>
       <c r="B209" s="5"/>
       <c r="C209" s="33" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D209" s="32" t="s">
         <v>58</v>
       </c>
       <c r="E209" s="32"/>
       <c r="F209" s="32" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="G209" s="6" t="s">
         <v>15</v>
@@ -6809,7 +6809,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="4"/>
       <c r="B210" s="5"/>
       <c r="C210" s="33"/>
@@ -6819,7 +6819,7 @@
       <c r="G210" s="6"/>
       <c r="H210" s="7"/>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="4"/>
       <c r="B211" s="5"/>
       <c r="C211" s="33"/>
@@ -6829,7 +6829,7 @@
       <c r="G211" s="6"/>
       <c r="H211" s="7"/>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="4"/>
       <c r="B212" s="5"/>
       <c r="C212" s="33"/>
@@ -6839,7 +6839,7 @@
       <c r="G212" s="6"/>
       <c r="H212" s="7"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="4"/>
       <c r="B213" s="5"/>
       <c r="C213" s="33"/>
@@ -6849,7 +6849,7 @@
       <c r="G213" s="6"/>
       <c r="H213" s="7"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="4"/>
       <c r="B214" s="5"/>
       <c r="C214" s="33"/>
@@ -6859,7 +6859,7 @@
       <c r="G214" s="6"/>
       <c r="H214" s="7"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="4"/>
       <c r="B215" s="5"/>
       <c r="C215" s="33"/>
@@ -6869,7 +6869,7 @@
       <c r="G215" s="6"/>
       <c r="H215" s="7"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="4"/>
       <c r="B216" s="5"/>
       <c r="C216" s="33"/>
@@ -6879,7 +6879,7 @@
       <c r="G216" s="6"/>
       <c r="H216" s="7"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="4"/>
       <c r="B217" s="5"/>
       <c r="C217" s="33"/>
@@ -6889,7 +6889,7 @@
       <c r="G217" s="6"/>
       <c r="H217" s="7"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="4"/>
       <c r="B218" s="5"/>
       <c r="C218" s="33"/>
@@ -6899,7 +6899,7 @@
       <c r="G218" s="6"/>
       <c r="H218" s="7"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="4"/>
       <c r="B219" s="5"/>
       <c r="C219" s="33"/>
@@ -6909,7 +6909,7 @@
       <c r="G219" s="6"/>
       <c r="H219" s="7"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="4"/>
       <c r="B220" s="5"/>
       <c r="C220" s="33"/>
@@ -6919,7 +6919,7 @@
       <c r="G220" s="6"/>
       <c r="H220" s="7"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="4"/>
       <c r="B221" s="5"/>
       <c r="C221" s="33"/>
@@ -6929,7 +6929,7 @@
       <c r="G221" s="6"/>
       <c r="H221" s="7"/>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="4"/>
       <c r="B222" s="5"/>
       <c r="C222" s="33"/>
@@ -6939,7 +6939,7 @@
       <c r="G222" s="6"/>
       <c r="H222" s="7"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="4"/>
       <c r="B223" s="5"/>
       <c r="C223" s="33"/>
@@ -6949,7 +6949,7 @@
       <c r="G223" s="6"/>
       <c r="H223" s="7"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="4"/>
       <c r="B224" s="5"/>
       <c r="C224" s="33"/>
@@ -6959,7 +6959,7 @@
       <c r="G224" s="6"/>
       <c r="H224" s="7"/>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="4"/>
       <c r="B225" s="5"/>
       <c r="C225" s="33"/>
@@ -6969,7 +6969,7 @@
       <c r="G225" s="6"/>
       <c r="H225" s="7"/>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="4"/>
       <c r="B226" s="5"/>
       <c r="C226" s="33"/>
@@ -6979,7 +6979,7 @@
       <c r="G226" s="6"/>
       <c r="H226" s="7"/>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" s="4"/>
       <c r="B227" s="5"/>
       <c r="C227" s="33"/>
@@ -6989,7 +6989,7 @@
       <c r="G227" s="6"/>
       <c r="H227" s="7"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="4"/>
       <c r="B228" s="5"/>
       <c r="C228" s="33"/>
@@ -6999,7 +6999,7 @@
       <c r="G228" s="6"/>
       <c r="H228" s="7"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="4"/>
       <c r="B229" s="5"/>
       <c r="C229" s="33"/>
@@ -7009,7 +7009,7 @@
       <c r="G229" s="6"/>
       <c r="H229" s="7"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="4"/>
       <c r="B230" s="5"/>
       <c r="C230" s="33"/>
@@ -7019,7 +7019,7 @@
       <c r="G230" s="6"/>
       <c r="H230" s="7"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="4"/>
       <c r="B231" s="5"/>
       <c r="C231" s="33"/>
@@ -7029,7 +7029,7 @@
       <c r="G231" s="6"/>
       <c r="H231" s="7"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="4"/>
       <c r="B232" s="5"/>
       <c r="C232" s="33"/>
@@ -7039,7 +7039,7 @@
       <c r="G232" s="6"/>
       <c r="H232" s="7"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="4"/>
       <c r="B233" s="5"/>
       <c r="C233" s="33"/>
@@ -7049,7 +7049,7 @@
       <c r="G233" s="6"/>
       <c r="H233" s="7"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="4"/>
       <c r="B234" s="5"/>
       <c r="C234" s="33"/>
@@ -7059,7 +7059,7 @@
       <c r="G234" s="6"/>
       <c r="H234" s="7"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="4"/>
       <c r="B235" s="5"/>
       <c r="C235" s="33"/>
@@ -7069,7 +7069,7 @@
       <c r="G235" s="6"/>
       <c r="H235" s="7"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="4"/>
       <c r="B236" s="5"/>
       <c r="C236" s="33"/>
@@ -7079,7 +7079,7 @@
       <c r="G236" s="6"/>
       <c r="H236" s="7"/>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="4"/>
       <c r="B237" s="5"/>
       <c r="C237" s="33"/>
@@ -7089,7 +7089,7 @@
       <c r="G237" s="6"/>
       <c r="H237" s="7"/>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" s="4"/>
       <c r="B238" s="5"/>
       <c r="C238" s="33"/>
@@ -7099,7 +7099,7 @@
       <c r="G238" s="6"/>
       <c r="H238" s="7"/>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="4"/>
       <c r="B239" s="5"/>
       <c r="C239" s="33"/>
@@ -7109,7 +7109,7 @@
       <c r="G239" s="6"/>
       <c r="H239" s="7"/>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" s="4"/>
       <c r="B240" s="5"/>
       <c r="C240" s="33"/>
@@ -7119,7 +7119,7 @@
       <c r="G240" s="6"/>
       <c r="H240" s="7"/>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="4"/>
       <c r="B241" s="5"/>
       <c r="C241" s="33"/>
@@ -7129,7 +7129,7 @@
       <c r="G241" s="6"/>
       <c r="H241" s="7"/>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" s="4"/>
       <c r="B242" s="5"/>
       <c r="C242" s="33"/>
@@ -7139,7 +7139,7 @@
       <c r="G242" s="6"/>
       <c r="H242" s="7"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="4"/>
       <c r="B243" s="5"/>
       <c r="C243" s="33"/>
@@ -7149,7 +7149,7 @@
       <c r="G243" s="6"/>
       <c r="H243" s="7"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="4"/>
       <c r="B244" s="5"/>
       <c r="C244" s="33"/>
@@ -7159,7 +7159,7 @@
       <c r="G244" s="6"/>
       <c r="H244" s="7"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="4"/>
       <c r="B245" s="5"/>
       <c r="C245" s="33"/>
@@ -7169,7 +7169,7 @@
       <c r="G245" s="6"/>
       <c r="H245" s="7"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="4"/>
       <c r="B246" s="5"/>
       <c r="C246" s="33"/>
@@ -7179,7 +7179,7 @@
       <c r="G246" s="6"/>
       <c r="H246" s="7"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="4"/>
       <c r="B247" s="5"/>
       <c r="C247" s="33"/>
@@ -7189,7 +7189,7 @@
       <c r="G247" s="6"/>
       <c r="H247" s="7"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="4"/>
       <c r="B248" s="5"/>
       <c r="C248" s="33"/>
@@ -7199,7 +7199,7 @@
       <c r="G248" s="6"/>
       <c r="H248" s="7"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="4"/>
       <c r="B249" s="5"/>
       <c r="C249" s="33"/>
@@ -7209,7 +7209,7 @@
       <c r="G249" s="6"/>
       <c r="H249" s="7"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="4"/>
       <c r="B250" s="5"/>
       <c r="C250" s="33"/>
@@ -7219,7 +7219,7 @@
       <c r="G250" s="6"/>
       <c r="H250" s="7"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="4"/>
       <c r="B251" s="5"/>
       <c r="C251" s="33"/>
@@ -7229,7 +7229,7 @@
       <c r="G251" s="6"/>
       <c r="H251" s="7"/>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="4"/>
       <c r="B252" s="5"/>
       <c r="C252" s="33"/>
@@ -7239,7 +7239,7 @@
       <c r="G252" s="6"/>
       <c r="H252" s="7"/>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="4"/>
       <c r="B253" s="5"/>
       <c r="C253" s="33"/>
@@ -7249,7 +7249,7 @@
       <c r="G253" s="6"/>
       <c r="H253" s="7"/>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="4"/>
       <c r="B254" s="5"/>
       <c r="C254" s="33"/>
@@ -7259,7 +7259,7 @@
       <c r="G254" s="6"/>
       <c r="H254" s="7"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="4"/>
       <c r="B255" s="5"/>
       <c r="C255" s="33"/>
@@ -7269,7 +7269,7 @@
       <c r="G255" s="6"/>
       <c r="H255" s="7"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="4"/>
       <c r="B256" s="5"/>
       <c r="C256" s="33"/>
@@ -7279,7 +7279,7 @@
       <c r="G256" s="6"/>
       <c r="H256" s="7"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" s="4"/>
       <c r="B257" s="5"/>
       <c r="C257" s="33"/>
@@ -7289,7 +7289,7 @@
       <c r="G257" s="6"/>
       <c r="H257" s="7"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="4"/>
       <c r="B258" s="5"/>
       <c r="C258" s="33"/>
@@ -7299,7 +7299,7 @@
       <c r="G258" s="6"/>
       <c r="H258" s="7"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" s="4"/>
       <c r="B259" s="5"/>
       <c r="C259" s="33"/>
@@ -7309,7 +7309,7 @@
       <c r="G259" s="6"/>
       <c r="H259" s="7"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="4"/>
       <c r="B260" s="5"/>
       <c r="C260" s="33"/>
@@ -7319,7 +7319,7 @@
       <c r="G260" s="6"/>
       <c r="H260" s="7"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="4"/>
       <c r="B261" s="5"/>
       <c r="C261" s="33"/>
@@ -7329,7 +7329,7 @@
       <c r="G261" s="6"/>
       <c r="H261" s="7"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="4"/>
       <c r="B262" s="5"/>
       <c r="C262" s="33"/>
@@ -7339,7 +7339,7 @@
       <c r="G262" s="6"/>
       <c r="H262" s="7"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" s="4"/>
       <c r="B263" s="5"/>
       <c r="C263" s="33"/>
@@ -7349,7 +7349,7 @@
       <c r="G263" s="6"/>
       <c r="H263" s="7"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="4"/>
       <c r="B264" s="5"/>
       <c r="C264" s="33"/>
@@ -7359,7 +7359,7 @@
       <c r="G264" s="6"/>
       <c r="H264" s="7"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" s="4"/>
       <c r="B265" s="5"/>
       <c r="C265" s="33"/>
@@ -7369,7 +7369,7 @@
       <c r="G265" s="6"/>
       <c r="H265" s="7"/>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A266" s="4"/>
       <c r="B266" s="5"/>
       <c r="C266" s="33"/>
@@ -7379,7 +7379,7 @@
       <c r="G266" s="6"/>
       <c r="H266" s="7"/>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267" s="4"/>
       <c r="B267" s="5"/>
       <c r="C267" s="33"/>
@@ -7389,7 +7389,7 @@
       <c r="G267" s="6"/>
       <c r="H267" s="7"/>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A268" s="4"/>
       <c r="B268" s="5"/>
       <c r="C268" s="33"/>
@@ -7399,7 +7399,7 @@
       <c r="G268" s="6"/>
       <c r="H268" s="7"/>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A269" s="4"/>
       <c r="B269" s="5"/>
       <c r="C269" s="33"/>
@@ -7409,7 +7409,7 @@
       <c r="G269" s="6"/>
       <c r="H269" s="7"/>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A270" s="4"/>
       <c r="B270" s="5"/>
       <c r="C270" s="33"/>
@@ -7419,7 +7419,7 @@
       <c r="G270" s="6"/>
       <c r="H270" s="7"/>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271" s="4"/>
       <c r="B271" s="5"/>
       <c r="C271" s="33"/>
@@ -7429,7 +7429,7 @@
       <c r="G271" s="6"/>
       <c r="H271" s="7"/>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272" s="4"/>
       <c r="B272" s="5"/>
       <c r="C272" s="33"/>
@@ -7439,7 +7439,7 @@
       <c r="G272" s="6"/>
       <c r="H272" s="7"/>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A273" s="4"/>
       <c r="B273" s="5"/>
       <c r="C273" s="33"/>
@@ -7449,7 +7449,7 @@
       <c r="G273" s="6"/>
       <c r="H273" s="7"/>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A274" s="4"/>
       <c r="B274" s="5"/>
       <c r="C274" s="33"/>
@@ -7459,7 +7459,7 @@
       <c r="G274" s="6"/>
       <c r="H274" s="7"/>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A275" s="4"/>
       <c r="B275" s="5"/>
       <c r="C275" s="33"/>
@@ -7469,7 +7469,7 @@
       <c r="G275" s="6"/>
       <c r="H275" s="7"/>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A276" s="4"/>
       <c r="B276" s="5"/>
       <c r="C276" s="33"/>
@@ -7479,7 +7479,7 @@
       <c r="G276" s="6"/>
       <c r="H276" s="7"/>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A277" s="4"/>
       <c r="B277" s="5"/>
       <c r="C277" s="33"/>
@@ -7489,7 +7489,7 @@
       <c r="G277" s="6"/>
       <c r="H277" s="7"/>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A278" s="4"/>
       <c r="B278" s="5"/>
       <c r="C278" s="33"/>
@@ -7499,7 +7499,7 @@
       <c r="G278" s="6"/>
       <c r="H278" s="7"/>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A279" s="4"/>
       <c r="B279" s="5"/>
       <c r="C279" s="33"/>
@@ -7509,7 +7509,7 @@
       <c r="G279" s="6"/>
       <c r="H279" s="7"/>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A280" s="4"/>
       <c r="B280" s="5"/>
       <c r="C280" s="33"/>
@@ -7519,7 +7519,7 @@
       <c r="G280" s="6"/>
       <c r="H280" s="7"/>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A281" s="4"/>
       <c r="B281" s="5"/>
       <c r="C281" s="33"/>
@@ -7529,7 +7529,7 @@
       <c r="G281" s="6"/>
       <c r="H281" s="7"/>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A282" s="4"/>
       <c r="B282" s="5"/>
       <c r="C282" s="33"/>
@@ -7539,7 +7539,7 @@
       <c r="G282" s="6"/>
       <c r="H282" s="7"/>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A283" s="4"/>
       <c r="B283" s="5"/>
       <c r="C283" s="33"/>
@@ -7549,7 +7549,7 @@
       <c r="G283" s="6"/>
       <c r="H283" s="7"/>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A284" s="4"/>
       <c r="B284" s="5"/>
       <c r="C284" s="33"/>
@@ -7559,7 +7559,7 @@
       <c r="G284" s="6"/>
       <c r="H284" s="7"/>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A285" s="4"/>
       <c r="B285" s="5"/>
       <c r="C285" s="33"/>
@@ -7569,7 +7569,7 @@
       <c r="G285" s="6"/>
       <c r="H285" s="7"/>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A286" s="4"/>
       <c r="B286" s="5"/>
       <c r="C286" s="33"/>
@@ -7579,7 +7579,7 @@
       <c r="G286" s="6"/>
       <c r="H286" s="7"/>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A287" s="4"/>
       <c r="B287" s="5"/>
       <c r="C287" s="33"/>
@@ -7589,7 +7589,7 @@
       <c r="G287" s="6"/>
       <c r="H287" s="7"/>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A288" s="4"/>
       <c r="B288" s="5"/>
       <c r="C288" s="33"/>
@@ -7599,7 +7599,7 @@
       <c r="G288" s="6"/>
       <c r="H288" s="7"/>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A289" s="4"/>
       <c r="B289" s="5"/>
       <c r="C289" s="33"/>
@@ -7609,7 +7609,7 @@
       <c r="G289" s="6"/>
       <c r="H289" s="7"/>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A290" s="4"/>
       <c r="B290" s="5"/>
       <c r="C290" s="33"/>
@@ -7619,7 +7619,7 @@
       <c r="G290" s="6"/>
       <c r="H290" s="7"/>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A291" s="4"/>
       <c r="B291" s="5"/>
       <c r="C291" s="33"/>
@@ -7629,7 +7629,7 @@
       <c r="G291" s="6"/>
       <c r="H291" s="7"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A292" s="4"/>
       <c r="B292" s="5"/>
       <c r="C292" s="33"/>
@@ -7639,7 +7639,7 @@
       <c r="G292" s="6"/>
       <c r="H292" s="7"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A293" s="4"/>
       <c r="B293" s="5"/>
       <c r="C293" s="33"/>
@@ -7649,7 +7649,7 @@
       <c r="G293" s="6"/>
       <c r="H293" s="7"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A294" s="4"/>
       <c r="B294" s="5"/>
       <c r="C294" s="33"/>
@@ -7659,7 +7659,7 @@
       <c r="G294" s="6"/>
       <c r="H294" s="7"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A295" s="4"/>
       <c r="B295" s="5"/>
       <c r="C295" s="33"/>
@@ -7669,7 +7669,7 @@
       <c r="G295" s="6"/>
       <c r="H295" s="7"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A296" s="4"/>
       <c r="B296" s="5"/>
       <c r="C296" s="33"/>
@@ -7679,7 +7679,7 @@
       <c r="G296" s="6"/>
       <c r="H296" s="7"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A297" s="4"/>
       <c r="B297" s="5"/>
       <c r="C297" s="33"/>
@@ -7689,7 +7689,7 @@
       <c r="G297" s="6"/>
       <c r="H297" s="7"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A298" s="4"/>
       <c r="B298" s="5"/>
       <c r="C298" s="33"/>
@@ -7699,7 +7699,7 @@
       <c r="G298" s="6"/>
       <c r="H298" s="7"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A299" s="4"/>
       <c r="B299" s="5"/>
       <c r="C299" s="33"/>
@@ -7709,7 +7709,7 @@
       <c r="G299" s="6"/>
       <c r="H299" s="7"/>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A300" s="4"/>
       <c r="B300" s="5"/>
       <c r="C300" s="33"/>
@@ -7719,7 +7719,7 @@
       <c r="G300" s="6"/>
       <c r="H300" s="7"/>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A301" s="4"/>
       <c r="B301" s="5"/>
       <c r="C301" s="33"/>
@@ -7729,7 +7729,7 @@
       <c r="G301" s="6"/>
       <c r="H301" s="7"/>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A302" s="4"/>
       <c r="B302" s="5"/>
       <c r="C302" s="33"/>
@@ -7739,7 +7739,7 @@
       <c r="G302" s="6"/>
       <c r="H302" s="7"/>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A303" s="4"/>
       <c r="B303" s="5"/>
       <c r="C303" s="33"/>
@@ -7749,7 +7749,7 @@
       <c r="G303" s="6"/>
       <c r="H303" s="7"/>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A304" s="4"/>
       <c r="B304" s="5"/>
       <c r="C304" s="33"/>
@@ -7759,7 +7759,7 @@
       <c r="G304" s="6"/>
       <c r="H304" s="7"/>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A305" s="4"/>
       <c r="B305" s="5"/>
       <c r="C305" s="33"/>
@@ -7769,7 +7769,7 @@
       <c r="G305" s="6"/>
       <c r="H305" s="7"/>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A306" s="4"/>
       <c r="B306" s="5"/>
       <c r="C306" s="33"/>
@@ -7779,7 +7779,7 @@
       <c r="G306" s="6"/>
       <c r="H306" s="7"/>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A307" s="4"/>
       <c r="B307" s="5"/>
       <c r="C307" s="33"/>
@@ -7789,7 +7789,7 @@
       <c r="G307" s="6"/>
       <c r="H307" s="7"/>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A308" s="4"/>
       <c r="B308" s="5"/>
       <c r="C308" s="33"/>
@@ -7799,7 +7799,7 @@
       <c r="G308" s="6"/>
       <c r="H308" s="7"/>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A309" s="4"/>
       <c r="B309" s="5"/>
       <c r="C309" s="33"/>
@@ -7809,7 +7809,7 @@
       <c r="G309" s="6"/>
       <c r="H309" s="7"/>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A310" s="4"/>
       <c r="B310" s="5"/>
       <c r="C310" s="33"/>
@@ -7819,7 +7819,7 @@
       <c r="G310" s="6"/>
       <c r="H310" s="7"/>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A311" s="4"/>
       <c r="B311" s="5"/>
       <c r="C311" s="33"/>
@@ -7829,7 +7829,7 @@
       <c r="G311" s="6"/>
       <c r="H311" s="7"/>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A312" s="4"/>
       <c r="B312" s="5"/>
       <c r="C312" s="33"/>
@@ -7839,7 +7839,7 @@
       <c r="G312" s="6"/>
       <c r="H312" s="7"/>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A313" s="4"/>
       <c r="B313" s="5"/>
       <c r="C313" s="33"/>
@@ -7849,7 +7849,7 @@
       <c r="G313" s="6"/>
       <c r="H313" s="7"/>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A314" s="4"/>
       <c r="B314" s="5"/>
       <c r="C314" s="33"/>
@@ -7859,7 +7859,7 @@
       <c r="G314" s="6"/>
       <c r="H314" s="7"/>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A315" s="4"/>
       <c r="B315" s="5"/>
       <c r="C315" s="33"/>
@@ -7869,7 +7869,7 @@
       <c r="G315" s="6"/>
       <c r="H315" s="7"/>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A316" s="4"/>
       <c r="B316" s="5"/>
       <c r="C316" s="33"/>
@@ -7879,7 +7879,7 @@
       <c r="G316" s="6"/>
       <c r="H316" s="7"/>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A317" s="4"/>
       <c r="B317" s="5"/>
       <c r="C317" s="33"/>
@@ -7889,7 +7889,7 @@
       <c r="G317" s="6"/>
       <c r="H317" s="7"/>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A318" s="4"/>
       <c r="B318" s="5"/>
       <c r="C318" s="33"/>
@@ -7899,7 +7899,7 @@
       <c r="G318" s="6"/>
       <c r="H318" s="7"/>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A319" s="4"/>
       <c r="B319" s="5"/>
       <c r="C319" s="33"/>
@@ -7909,7 +7909,7 @@
       <c r="G319" s="6"/>
       <c r="H319" s="7"/>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A320" s="4"/>
       <c r="B320" s="5"/>
       <c r="C320" s="33"/>
@@ -7919,7 +7919,7 @@
       <c r="G320" s="6"/>
       <c r="H320" s="7"/>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A321" s="4"/>
       <c r="B321" s="5"/>
       <c r="C321" s="33"/>
@@ -7929,7 +7929,7 @@
       <c r="G321" s="6"/>
       <c r="H321" s="7"/>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A322" s="4"/>
       <c r="B322" s="5"/>
       <c r="C322" s="33"/>
@@ -7939,7 +7939,7 @@
       <c r="G322" s="6"/>
       <c r="H322" s="7"/>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A323" s="4"/>
       <c r="B323" s="5"/>
       <c r="C323" s="33"/>
@@ -7949,7 +7949,7 @@
       <c r="G323" s="6"/>
       <c r="H323" s="7"/>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A324" s="4"/>
       <c r="B324" s="5"/>
       <c r="C324" s="33"/>
@@ -7959,7 +7959,7 @@
       <c r="G324" s="6"/>
       <c r="H324" s="7"/>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A325" s="4"/>
       <c r="B325" s="5"/>
       <c r="C325" s="33"/>
@@ -7969,7 +7969,7 @@
       <c r="G325" s="6"/>
       <c r="H325" s="7"/>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A326" s="4"/>
       <c r="B326" s="5"/>
       <c r="C326" s="33"/>
@@ -7979,7 +7979,7 @@
       <c r="G326" s="6"/>
       <c r="H326" s="7"/>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A327" s="4"/>
       <c r="B327" s="5"/>
       <c r="C327" s="33"/>
@@ -7989,7 +7989,7 @@
       <c r="G327" s="6"/>
       <c r="H327" s="7"/>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A328" s="4"/>
       <c r="B328" s="5"/>
       <c r="C328" s="33"/>
@@ -7999,7 +7999,7 @@
       <c r="G328" s="6"/>
       <c r="H328" s="7"/>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A329" s="4"/>
       <c r="B329" s="5"/>
       <c r="C329" s="33"/>
@@ -8009,7 +8009,7 @@
       <c r="G329" s="6"/>
       <c r="H329" s="7"/>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A330" s="4"/>
       <c r="B330" s="5"/>
       <c r="C330" s="33"/>
@@ -8019,7 +8019,7 @@
       <c r="G330" s="6"/>
       <c r="H330" s="7"/>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A331" s="4"/>
       <c r="B331" s="5"/>
       <c r="C331" s="33"/>
@@ -8029,7 +8029,7 @@
       <c r="G331" s="6"/>
       <c r="H331" s="7"/>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A332" s="4"/>
       <c r="B332" s="5"/>
       <c r="C332" s="33"/>
@@ -8039,7 +8039,7 @@
       <c r="G332" s="6"/>
       <c r="H332" s="7"/>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A333" s="4"/>
       <c r="B333" s="5"/>
       <c r="C333" s="33"/>
@@ -8049,7 +8049,7 @@
       <c r="G333" s="6"/>
       <c r="H333" s="7"/>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A334" s="4"/>
       <c r="B334" s="5"/>
       <c r="C334" s="33"/>
@@ -8059,7 +8059,7 @@
       <c r="G334" s="6"/>
       <c r="H334" s="7"/>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A335" s="4"/>
       <c r="B335" s="5"/>
       <c r="C335" s="33"/>
@@ -8069,7 +8069,7 @@
       <c r="G335" s="6"/>
       <c r="H335" s="7"/>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" s="4"/>
       <c r="B336" s="5"/>
       <c r="C336" s="33"/>
@@ -8079,7 +8079,7 @@
       <c r="G336" s="6"/>
       <c r="H336" s="7"/>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" s="4"/>
       <c r="B337" s="5"/>
       <c r="C337" s="33"/>
@@ -8089,7 +8089,7 @@
       <c r="G337" s="6"/>
       <c r="H337" s="7"/>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" s="4"/>
       <c r="B338" s="5"/>
       <c r="C338" s="33"/>
@@ -8099,7 +8099,7 @@
       <c r="G338" s="6"/>
       <c r="H338" s="7"/>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" s="4"/>
       <c r="B339" s="5"/>
       <c r="C339" s="33"/>
@@ -8109,7 +8109,7 @@
       <c r="G339" s="6"/>
       <c r="H339" s="7"/>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" s="4"/>
       <c r="B340" s="5"/>
       <c r="C340" s="33"/>
@@ -8119,7 +8119,7 @@
       <c r="G340" s="6"/>
       <c r="H340" s="7"/>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" s="4"/>
       <c r="B341" s="5"/>
       <c r="C341" s="33"/>
@@ -8129,7 +8129,7 @@
       <c r="G341" s="6"/>
       <c r="H341" s="7"/>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" s="4"/>
       <c r="B342" s="5"/>
       <c r="C342" s="33"/>
@@ -8139,7 +8139,7 @@
       <c r="G342" s="6"/>
       <c r="H342" s="7"/>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" s="4"/>
       <c r="B343" s="5"/>
       <c r="C343" s="33"/>
@@ -8149,7 +8149,7 @@
       <c r="G343" s="6"/>
       <c r="H343" s="7"/>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" s="4"/>
       <c r="B344" s="5"/>
       <c r="C344" s="33"/>
@@ -8159,7 +8159,7 @@
       <c r="G344" s="6"/>
       <c r="H344" s="7"/>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" s="4"/>
       <c r="B345" s="5"/>
       <c r="C345" s="33"/>
@@ -8169,7 +8169,7 @@
       <c r="G345" s="6"/>
       <c r="H345" s="7"/>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A346" s="4"/>
       <c r="B346" s="5"/>
       <c r="C346" s="33"/>
@@ -8179,7 +8179,7 @@
       <c r="G346" s="6"/>
       <c r="H346" s="7"/>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A347" s="4"/>
       <c r="B347" s="5"/>
       <c r="C347" s="33"/>
@@ -8189,7 +8189,7 @@
       <c r="G347" s="6"/>
       <c r="H347" s="7"/>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A348" s="4"/>
       <c r="B348" s="5"/>
       <c r="C348" s="33"/>
@@ -8199,7 +8199,7 @@
       <c r="G348" s="6"/>
       <c r="H348" s="7"/>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A349" s="4"/>
       <c r="B349" s="5"/>
       <c r="C349" s="33"/>
@@ -8209,7 +8209,7 @@
       <c r="G349" s="6"/>
       <c r="H349" s="7"/>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A350" s="4"/>
       <c r="B350" s="5"/>
       <c r="C350" s="33"/>
@@ -8219,7 +8219,7 @@
       <c r="G350" s="6"/>
       <c r="H350" s="7"/>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" s="4"/>
       <c r="B351" s="5"/>
       <c r="C351" s="33"/>
@@ -8229,7 +8229,7 @@
       <c r="G351" s="6"/>
       <c r="H351" s="7"/>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" s="4"/>
       <c r="B352" s="5"/>
       <c r="C352" s="33"/>
@@ -8239,7 +8239,7 @@
       <c r="G352" s="6"/>
       <c r="H352" s="7"/>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" s="4"/>
       <c r="B353" s="5"/>
       <c r="C353" s="33"/>
@@ -8249,7 +8249,7 @@
       <c r="G353" s="6"/>
       <c r="H353" s="7"/>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" s="4"/>
       <c r="B354" s="5"/>
       <c r="C354" s="33"/>
@@ -8259,7 +8259,7 @@
       <c r="G354" s="6"/>
       <c r="H354" s="7"/>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" s="4"/>
       <c r="B355" s="5"/>
       <c r="C355" s="33"/>
@@ -8269,7 +8269,7 @@
       <c r="G355" s="6"/>
       <c r="H355" s="7"/>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" s="4"/>
       <c r="B356" s="5"/>
       <c r="C356" s="33"/>
@@ -8279,7 +8279,7 @@
       <c r="G356" s="6"/>
       <c r="H356" s="7"/>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" s="4"/>
       <c r="B357" s="5"/>
       <c r="C357" s="33"/>
@@ -8289,7 +8289,7 @@
       <c r="G357" s="6"/>
       <c r="H357" s="7"/>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" s="4"/>
       <c r="B358" s="5"/>
       <c r="C358" s="33"/>
@@ -8299,7 +8299,7 @@
       <c r="G358" s="6"/>
       <c r="H358" s="7"/>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" s="4"/>
       <c r="B359" s="5"/>
       <c r="C359" s="33"/>
@@ -8309,7 +8309,7 @@
       <c r="G359" s="6"/>
       <c r="H359" s="7"/>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" s="4"/>
       <c r="B360" s="5"/>
       <c r="C360" s="33"/>
@@ -8319,7 +8319,7 @@
       <c r="G360" s="6"/>
       <c r="H360" s="7"/>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" s="4"/>
       <c r="B361" s="5"/>
       <c r="C361" s="33"/>
@@ -8329,7 +8329,7 @@
       <c r="G361" s="6"/>
       <c r="H361" s="7"/>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" s="4"/>
       <c r="B362" s="5"/>
       <c r="C362" s="33"/>
@@ -8339,7 +8339,7 @@
       <c r="G362" s="6"/>
       <c r="H362" s="7"/>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" s="4"/>
       <c r="B363" s="5"/>
       <c r="C363" s="33"/>
@@ -8349,7 +8349,7 @@
       <c r="G363" s="6"/>
       <c r="H363" s="7"/>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" s="4"/>
       <c r="B364" s="5"/>
       <c r="C364" s="33"/>
@@ -8359,7 +8359,7 @@
       <c r="G364" s="6"/>
       <c r="H364" s="7"/>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" s="4"/>
       <c r="B365" s="5"/>
       <c r="C365" s="33"/>
@@ -8369,7 +8369,7 @@
       <c r="G365" s="6"/>
       <c r="H365" s="7"/>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" s="4"/>
       <c r="B366" s="5"/>
       <c r="C366" s="33"/>
@@ -8379,7 +8379,7 @@
       <c r="G366" s="6"/>
       <c r="H366" s="7"/>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" s="4"/>
       <c r="B367" s="5"/>
       <c r="C367" s="33"/>
@@ -8389,7 +8389,7 @@
       <c r="G367" s="6"/>
       <c r="H367" s="7"/>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A368" s="4"/>
       <c r="B368" s="5"/>
       <c r="C368" s="33"/>
@@ -8399,7 +8399,7 @@
       <c r="G368" s="6"/>
       <c r="H368" s="7"/>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" s="4"/>
       <c r="B369" s="5"/>
       <c r="C369" s="33"/>
@@ -8409,7 +8409,7 @@
       <c r="G369" s="6"/>
       <c r="H369" s="7"/>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" s="4"/>
       <c r="B370" s="5"/>
       <c r="C370" s="33"/>
@@ -8419,7 +8419,7 @@
       <c r="G370" s="6"/>
       <c r="H370" s="7"/>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" s="4"/>
       <c r="B371" s="5"/>
       <c r="C371" s="33"/>
@@ -8429,7 +8429,7 @@
       <c r="G371" s="6"/>
       <c r="H371" s="7"/>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A372" s="4"/>
       <c r="B372" s="5"/>
       <c r="C372" s="33"/>
@@ -8439,7 +8439,7 @@
       <c r="G372" s="6"/>
       <c r="H372" s="7"/>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" s="4"/>
       <c r="B373" s="5"/>
       <c r="C373" s="33"/>
@@ -8449,7 +8449,7 @@
       <c r="G373" s="6"/>
       <c r="H373" s="7"/>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A374" s="4"/>
       <c r="B374" s="5"/>
       <c r="C374" s="33"/>
@@ -8459,7 +8459,7 @@
       <c r="G374" s="6"/>
       <c r="H374" s="7"/>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A375" s="4"/>
       <c r="B375" s="5"/>
       <c r="C375" s="33"/>
@@ -8469,7 +8469,7 @@
       <c r="G375" s="6"/>
       <c r="H375" s="7"/>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A376" s="4"/>
       <c r="B376" s="5"/>
       <c r="C376" s="33"/>
@@ -8479,7 +8479,7 @@
       <c r="G376" s="6"/>
       <c r="H376" s="7"/>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A377" s="4"/>
       <c r="B377" s="5"/>
       <c r="C377" s="33"/>
@@ -8489,7 +8489,7 @@
       <c r="G377" s="6"/>
       <c r="H377" s="7"/>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A378" s="4"/>
       <c r="B378" s="5"/>
       <c r="C378" s="33"/>
@@ -8499,7 +8499,7 @@
       <c r="G378" s="6"/>
       <c r="H378" s="7"/>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A379" s="4"/>
       <c r="B379" s="5"/>
       <c r="C379" s="33"/>
@@ -8509,7 +8509,7 @@
       <c r="G379" s="6"/>
       <c r="H379" s="7"/>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A380" s="4"/>
       <c r="B380" s="5"/>
       <c r="C380" s="33"/>
@@ -8519,7 +8519,7 @@
       <c r="G380" s="6"/>
       <c r="H380" s="7"/>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A381" s="4"/>
       <c r="B381" s="5"/>
       <c r="C381" s="33"/>
@@ -8529,7 +8529,7 @@
       <c r="G381" s="6"/>
       <c r="H381" s="7"/>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A382" s="4"/>
       <c r="B382" s="5"/>
       <c r="C382" s="33"/>
@@ -8539,7 +8539,7 @@
       <c r="G382" s="6"/>
       <c r="H382" s="7"/>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A383" s="4"/>
       <c r="B383" s="5"/>
       <c r="C383" s="33"/>
@@ -8549,7 +8549,7 @@
       <c r="G383" s="6"/>
       <c r="H383" s="7"/>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A384" s="4"/>
       <c r="B384" s="5"/>
       <c r="C384" s="33"/>
@@ -8559,7 +8559,7 @@
       <c r="G384" s="6"/>
       <c r="H384" s="7"/>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A385" s="4"/>
       <c r="B385" s="5"/>
       <c r="C385" s="33"/>
@@ -8569,7 +8569,7 @@
       <c r="G385" s="6"/>
       <c r="H385" s="7"/>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A386" s="4"/>
       <c r="B386" s="5"/>
       <c r="C386" s="33"/>
@@ -8579,7 +8579,7 @@
       <c r="G386" s="6"/>
       <c r="H386" s="7"/>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A387" s="4"/>
       <c r="B387" s="5"/>
       <c r="C387" s="33"/>
@@ -8589,7 +8589,7 @@
       <c r="G387" s="6"/>
       <c r="H387" s="7"/>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A388" s="4"/>
       <c r="B388" s="5"/>
       <c r="C388" s="33"/>
@@ -8599,7 +8599,7 @@
       <c r="G388" s="6"/>
       <c r="H388" s="7"/>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A389" s="4"/>
       <c r="B389" s="5"/>
       <c r="C389" s="33"/>
@@ -8609,7 +8609,7 @@
       <c r="G389" s="6"/>
       <c r="H389" s="7"/>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A390" s="4"/>
       <c r="B390" s="5"/>
       <c r="C390" s="33"/>
@@ -8619,7 +8619,7 @@
       <c r="G390" s="6"/>
       <c r="H390" s="7"/>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A391" s="4"/>
       <c r="B391" s="5"/>
       <c r="C391" s="33"/>
@@ -8629,7 +8629,7 @@
       <c r="G391" s="6"/>
       <c r="H391" s="7"/>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A392" s="4"/>
       <c r="B392" s="5"/>
       <c r="C392" s="33"/>
@@ -8639,7 +8639,7 @@
       <c r="G392" s="6"/>
       <c r="H392" s="7"/>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A393" s="4"/>
       <c r="B393" s="5"/>
       <c r="C393" s="33"/>
@@ -8649,7 +8649,7 @@
       <c r="G393" s="6"/>
       <c r="H393" s="7"/>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A394" s="4"/>
       <c r="B394" s="5"/>
       <c r="C394" s="33"/>
@@ -8659,7 +8659,7 @@
       <c r="G394" s="6"/>
       <c r="H394" s="7"/>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A395" s="4"/>
       <c r="B395" s="5"/>
       <c r="C395" s="33"/>
@@ -8669,7 +8669,7 @@
       <c r="G395" s="6"/>
       <c r="H395" s="7"/>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A396" s="4"/>
       <c r="B396" s="5"/>
       <c r="C396" s="33"/>
@@ -8679,7 +8679,7 @@
       <c r="G396" s="6"/>
       <c r="H396" s="7"/>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A397" s="4"/>
       <c r="B397" s="5"/>
       <c r="C397" s="33"/>
@@ -8689,7 +8689,7 @@
       <c r="G397" s="6"/>
       <c r="H397" s="7"/>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A398" s="4"/>
       <c r="B398" s="5"/>
       <c r="C398" s="33"/>
@@ -8699,7 +8699,7 @@
       <c r="G398" s="6"/>
       <c r="H398" s="7"/>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A399" s="4"/>
       <c r="B399" s="5"/>
       <c r="C399" s="33"/>
@@ -8709,7 +8709,7 @@
       <c r="G399" s="6"/>
       <c r="H399" s="7"/>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A400" s="4"/>
       <c r="B400" s="5"/>
       <c r="C400" s="33"/>
@@ -8719,7 +8719,7 @@
       <c r="G400" s="6"/>
       <c r="H400" s="7"/>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A401" s="4"/>
       <c r="B401" s="5"/>
       <c r="C401" s="33"/>
@@ -8729,7 +8729,7 @@
       <c r="G401" s="6"/>
       <c r="H401" s="7"/>
     </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A402" s="4"/>
       <c r="B402" s="5"/>
       <c r="C402" s="33"/>
@@ -8739,7 +8739,7 @@
       <c r="G402" s="6"/>
       <c r="H402" s="7"/>
     </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A403" s="4"/>
       <c r="B403" s="5"/>
       <c r="C403" s="33"/>
@@ -8749,7 +8749,7 @@
       <c r="G403" s="6"/>
       <c r="H403" s="7"/>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A404" s="4"/>
       <c r="B404" s="5"/>
       <c r="C404" s="33"/>
@@ -8759,7 +8759,7 @@
       <c r="G404" s="6"/>
       <c r="H404" s="7"/>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A405" s="4"/>
       <c r="B405" s="5"/>
       <c r="C405" s="33"/>
@@ -8769,7 +8769,7 @@
       <c r="G405" s="6"/>
       <c r="H405" s="7"/>
     </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A406" s="4"/>
       <c r="B406" s="5"/>
       <c r="C406" s="33"/>
@@ -8779,7 +8779,7 @@
       <c r="G406" s="6"/>
       <c r="H406" s="7"/>
     </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A407" s="4"/>
       <c r="B407" s="5"/>
       <c r="C407" s="33"/>
@@ -8789,7 +8789,7 @@
       <c r="G407" s="6"/>
       <c r="H407" s="7"/>
     </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A408" s="4"/>
       <c r="B408" s="5"/>
       <c r="C408" s="33"/>
@@ -8799,7 +8799,7 @@
       <c r="G408" s="6"/>
       <c r="H408" s="7"/>
     </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A409" s="4"/>
       <c r="B409" s="5"/>
       <c r="C409" s="33"/>
@@ -8809,7 +8809,7 @@
       <c r="G409" s="6"/>
       <c r="H409" s="7"/>
     </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A410" s="4"/>
       <c r="B410" s="5"/>
       <c r="C410" s="33"/>
@@ -8819,7 +8819,7 @@
       <c r="G410" s="6"/>
       <c r="H410" s="7"/>
     </row>
-    <row r="411" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A411" s="8"/>
       <c r="B411" s="9"/>
       <c r="C411" s="10"/>
@@ -8829,7 +8829,7 @@
       <c r="G411" s="12"/>
       <c r="H411" s="13"/>
     </row>
-    <row r="1048576" spans="7:8" x14ac:dyDescent="0.35">
+    <row r="1048576" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G1048576" s="2"/>
       <c r="H1048576" s="2"/>
     </row>
@@ -8878,37 +8878,37 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -8929,12 +8929,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001733C14AC8EC6F498F123411DB8BC020" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c1f196d61ef494b6c4f62f58be5bb14e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7b7cc8fe-90e2-43f3-ad3c-00f457ec8258" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="46c76a5a58717c3453de3c52cd271f55" ns2:_="">
     <xsd:import namespace="7b7cc8fe-90e2-43f3-ad3c-00f457ec8258"/>
@@ -9066,6 +9060,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53ACD002-FFBE-4185-9DDB-0AA3A824C3C1}">
   <ds:schemaRefs>
@@ -9075,15 +9075,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7ACA6411-41A0-4B6C-874D-1FC05CC4B568}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE70D9AC-1270-4AD5-BB63-23D2B0A32B51}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9099,4 +9090,13 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7ACA6411-41A0-4B6C-874D-1FC05CC4B568}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>